--- a/docs/xlsx/jobs-2026-09-10.xlsx
+++ b/docs/xlsx/jobs-2026-09-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="567">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,1089 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Lake Tahoe Wildlife Care</t>
+  </si>
+  <si>
+    <t>South Lake Tahoe, CA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$17 - $18.50 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-administrative-assistant-south-lake-tahoe-california/1739773073</t>
+  </si>
+  <si>
+    <t>Agriculture Projects Coordinator</t>
+  </si>
+  <si>
+    <t>Alliance for the Chesapeake Bay</t>
+  </si>
+  <si>
+    <t>Lancaster, PA</t>
+  </si>
+  <si>
+    <t>$52,000 - $57,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-agriculture-projects-coordinator-lancaster-pennsylvania/3828019289</t>
+  </si>
+  <si>
+    <t>Animal Care Specialist</t>
+  </si>
+  <si>
+    <t>Navarre Beach Sea Turtle Conservation Center</t>
+  </si>
+  <si>
+    <t>Navarre, FL</t>
+  </si>
+  <si>
+    <t>$30,000 per year</t>
+  </si>
+  <si>
+    <t>marine-biology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-animal-care-specialist-navarre-florida/2512855578</t>
+  </si>
+  <si>
+    <t>Assistant Director of Development</t>
+  </si>
+  <si>
+    <t>Essex County Greenbelt Assoc</t>
+  </si>
+  <si>
+    <t>Essex, MA</t>
+  </si>
+  <si>
+    <t>$75,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-director-of-development-essex-massachusetts/4593727564</t>
+  </si>
+  <si>
+    <t>Classroom-Based Educator - Wheat Week Program (Spokane County)</t>
+  </si>
+  <si>
+    <t>Franklin Conservation District</t>
+  </si>
+  <si>
+    <t>Spokane, WA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$23 - $25 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-classroom-based-educator---wheat-week-program-spokane-county-spokane-washington/3472137620</t>
+  </si>
+  <si>
+    <t>Community Programs Coordinator</t>
+  </si>
+  <si>
+    <t>Lake Tahoe Wildlife Center</t>
+  </si>
+  <si>
+    <t>$20 - $22 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-programs-coordinator-south-lake-tahoe-california/3344294292</t>
+  </si>
+  <si>
+    <t>Development &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>$24 - $28 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development--communications-manager-south-lake-tahoe-california/8892879526</t>
+  </si>
+  <si>
+    <t>Education &amp; Outreach Specialist</t>
+  </si>
+  <si>
+    <t>Antrim Conservation District</t>
+  </si>
+  <si>
+    <t>Bellaire, MI</t>
+  </si>
+  <si>
+    <t>$20 - $25 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education--outreach-specialist-bellaire-michigan/4720425954</t>
+  </si>
+  <si>
+    <t>Environmental Education &amp; Communications Associate</t>
+  </si>
+  <si>
+    <t>Westmoreland Sanctuary, Inc.</t>
+  </si>
+  <si>
+    <t>Mount Kisco, NY</t>
+  </si>
+  <si>
+    <t>$45,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-communications--education-associate-mount-kisco-new-york/4693176563</t>
+  </si>
+  <si>
+    <t>EPA Development of Computational Approaches for Predicting Thyroid Systems Disruption in Aquatic Species</t>
+  </si>
+  <si>
+    <t>U.S. Environmental Protection Agency (EPA)</t>
+  </si>
+  <si>
+    <t>Duluth, MN</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>Stipend $50,460.00 – $61,722.00 Yearly</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-epa-development-of-computational-approaches-for-predicting-thyroid-systems-disruption-in-aquatic-species-duluth-minnesota/3314320797</t>
+  </si>
+  <si>
+    <t>EPA Quantitative Bioassay Development for Aquatic Vertebrates</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-epa-quantitative-bioassay-development-for-aquatic-vertebrates-duluth-minnesota/7374519556</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>The Kennebec Land Trust</t>
+  </si>
+  <si>
+    <t>Winthrop, ME</t>
+  </si>
+  <si>
+    <t>$87,000 - $106,200 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-winthrop-maine/9262620442</t>
+  </si>
+  <si>
+    <t>Wild Whatcom</t>
+  </si>
+  <si>
+    <t>Bellingham, WA</t>
+  </si>
+  <si>
+    <t>$85,000 - $105,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>Idealist</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-bellingham-washington/5184730052</t>
+  </si>
+  <si>
+    <t>Mountain Area Land Trust</t>
+  </si>
+  <si>
+    <t>Evergreen, CO</t>
+  </si>
+  <si>
+    <t>$108,000 - $125,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-evergreen-colorado/3293340986</t>
+  </si>
+  <si>
+    <t>Gift Processing Specialist</t>
+  </si>
+  <si>
+    <t>Pheasants Forever and Quail Forever</t>
+  </si>
+  <si>
+    <t>St. Paul, MN</t>
+  </si>
+  <si>
+    <t>$49,300 - $61,600 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-gift-processing-specialist-st-paul-minnesota/1733364286</t>
+  </si>
+  <si>
+    <t>GIS &amp; Information Systems Administrator</t>
+  </si>
+  <si>
+    <t>Great Redwood Trail Agency</t>
+  </si>
+  <si>
+    <t>Remote, CA</t>
+  </si>
+  <si>
+    <t>$80,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-gis--information-systems-administrator-remote-in-california/4908768628</t>
+  </si>
+  <si>
+    <t>Grants Administrator</t>
+  </si>
+  <si>
+    <t>National Association of Conservation Districts’ (NACD)</t>
+  </si>
+  <si>
+    <t>Washington DC, Remote</t>
+  </si>
+  <si>
+    <t>$65,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grants-administrator-washington-dc-remote/8100533024</t>
+  </si>
+  <si>
+    <t>Habitat Specialist</t>
+  </si>
+  <si>
+    <t>Columbia, SC</t>
+  </si>
+  <si>
+    <t>$40,000 - $44,000 per year</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-habitat-specialist-columbia-south-carolina/6232070676</t>
+  </si>
+  <si>
+    <t>Land Use Coordinator</t>
+  </si>
+  <si>
+    <t>Town of Sunapee</t>
+  </si>
+  <si>
+    <t>Sunapee, NH</t>
+  </si>
+  <si>
+    <t>$55,800 - $63,200 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-use-coordinator-sunapee-new-hampshire/1099736614</t>
+  </si>
+  <si>
+    <t>Paid Marine Science Education Internship</t>
+  </si>
+  <si>
+    <t>The Pigeon Key Foundation</t>
+  </si>
+  <si>
+    <t>Marathon, FL</t>
+  </si>
+  <si>
+    <t>$1,000 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-paid-marine-science-education-internship-marathon-florida/9961415754</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>New March Strategies</t>
+  </si>
+  <si>
+    <t>Madison (Remote), WI</t>
+  </si>
+  <si>
+    <t>The starting salary for this position is $70,000 (but is negotiable based on experience and qualifications).</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-admin-leadership-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-project-manager-madison-wisconsin/7536457779</t>
+  </si>
+  <si>
+    <t>Property Coordinator</t>
+  </si>
+  <si>
+    <t>Duxbury Beach Reservation, Inc.</t>
+  </si>
+  <si>
+    <t>Duxbury, MA</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-property-coordinator-duxbury-massachusetts/7066401621</t>
+  </si>
+  <si>
+    <t>Public Lands Manager</t>
+  </si>
+  <si>
+    <t>Methow Valley Citizens Council</t>
+  </si>
+  <si>
+    <t>Twisp, WA</t>
+  </si>
+  <si>
+    <t>$30 - $35 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-lands-manager-twisp-washington/3864955164</t>
+  </si>
+  <si>
+    <t>Rural Sustainability Manager</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-rural-sustainability-manager-twisp-washington/3879096340</t>
+  </si>
+  <si>
+    <t>Senior Management Analyst Reserve Management/Monitoring</t>
+  </si>
+  <si>
+    <t>Riverside County Transportation Commission</t>
+  </si>
+  <si>
+    <t>Riverside, CA</t>
+  </si>
+  <si>
+    <t>$9,923 - $13,397 per month</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-management-analyst-reserve-managementmonitoring-riverside-california/8115195007</t>
+  </si>
+  <si>
+    <t>Summer Camp Manager</t>
+  </si>
+  <si>
+    <t>Pocono Environmental Education Center</t>
+  </si>
+  <si>
+    <t>Dingmans Ferry, PA</t>
+  </si>
+  <si>
+    <t>$30,000 - $32,000 per year</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-summer-camp-manager-dingmans-ferry-pennsylvania/3543791079</t>
+  </si>
+  <si>
+    <t>Tenure Track Faculty of Biology and Forestry (26-54)</t>
+  </si>
+  <si>
+    <t>Francis Marion University</t>
+  </si>
+  <si>
+    <t>Florence, SC</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>Salary is commensurate with education and experience.</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tenure-track-faculty-of-biology-and-forestry-26-54-florence-south-carolina/6423228243</t>
+  </si>
+  <si>
+    <t>USDA-ARS Postdoctoral Research Fellowship in Agronomy/Plant Physiology</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture (USDA)</t>
+  </si>
+  <si>
+    <t>Stoneville, MS</t>
+  </si>
+  <si>
+    <t>Stipend $65,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-postdoctoral-research-fellowship-in-agronomyplant-physiology-stoneville-mississippi/2932569877</t>
+  </si>
+  <si>
+    <t>Vice President of Community Engagement</t>
+  </si>
+  <si>
+    <t>Conservation Colorado</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>$165,000 - $185,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vice-president-of-community-engagement-denver-colorado/5461863635</t>
+  </si>
+  <si>
+    <t>Academic Group Leader</t>
+  </si>
+  <si>
+    <t>Zone 126</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 18.00/hour</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5111e2e50e5145afa78b2053c80c2298-academic-group-leader-zone-126-queens-county</t>
+  </si>
+  <si>
+    <t>Academic Group Leader Middle School</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9bc1ef7d50144acc91b4332a12cd2330-academic-group-leader-middle-school-zone-126-queens-county</t>
+  </si>
+  <si>
+    <t>Accounting Manager (Full Time, Remote)</t>
+  </si>
+  <si>
+    <t>Accelerate Change</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e76bb226923a4cce9aeb9cef4b1cdc65-accounting-manager-full-time-remote-accelerate-change-washington</t>
+  </si>
+  <si>
+    <t>Activity Specialist</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e75f0cb7d884c6b9eb2f26bb3776965-activity-specialist-zone-126-queens-county</t>
+  </si>
+  <si>
+    <t>Administrative Associate</t>
+  </si>
+  <si>
+    <t>Vermont Foodbank</t>
+  </si>
+  <si>
+    <t>Barre, Vermont</t>
+  </si>
+  <si>
+    <t>USD 53570.00 - 58589.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Poverty, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/debf2bd54c234700adba520d46c73e64-administrative-associate-vermont-foodbank-barre</t>
+  </si>
+  <si>
+    <t>Admissions Director</t>
+  </si>
+  <si>
+    <t>MacDowell</t>
+  </si>
+  <si>
+    <t>Peterborough, New Hampshire</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73027f136b7c4f2a8ed0dbbf193bf010-admissions-director-macdowell-peterborough</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General- Counsel II</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/69ba2f3c108b4d6a86962af54c9741e8-assistant-attorney-general-counsel-ii-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Assistant Director, Events South Florida (preferably in Broward, Dade or South Palm Beach)</t>
+  </si>
+  <si>
+    <t>AJC</t>
+  </si>
+  <si>
+    <t>Palm Beach, Florida</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Human Rights Civil Liberties, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7fb9431a08084deda21d75452a78e31f-assistant-director-events-south-florida-preferably-in-broward-dade-or-south-palm-beach-ajc-palm-beach</t>
+  </si>
+  <si>
+    <t>Billing &amp; Legal Assistant (full-time) at Law Firm Exclusively Serving Nonproﬁt/Tax-Exempt Organizations</t>
+  </si>
+  <si>
+    <t>Cheshire Law Group</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/922715056e8f4328bc22eb0b9329e5a3-billing-legal-assistant-full-time-at-law-firm-exclusively-serving-nonprofittax-exempt-organizations-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
+    <t>Billing Assistant (part-time) at Law Firm Exclusively Serving Nonproﬁt/Tax-Exempt Organizations</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/631d92e2678a452d86418f62a5c08a54-billing-assistant-part-time-at-law-firm-exclusively-serving-nonprofittax-exempt-organizations-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
+    <t>Business Engagement Director</t>
+  </si>
+  <si>
+    <t>American Business Immigration Coalition</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ccde91fd3a264aa28504d86ae81d4509-business-engagement-director-american-business-immigration-coalition-chicago</t>
+  </si>
+  <si>
+    <t>Business Engagement Manager</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a99b793874848ed9e3dd7a64ded1394-business-engagement-manager-american-business-immigration-coalition-chicago</t>
+  </si>
+  <si>
+    <t>Canvasser</t>
+  </si>
+  <si>
+    <t>New Economic Justice Organizing Project</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 18.75 - 18.75/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/36092a14295f469a872545df2a7d1d88-canvasser-new-economic-justice-organizing-project-new-orleans</t>
+  </si>
+  <si>
+    <t>Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Potomac Conservancy</t>
+  </si>
+  <si>
+    <t>Bethesda, Maryland</t>
+  </si>
+  <si>
+    <t>USD 114000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da2816f25f694ce89be33412267b0f0d-chief-development-officer-potomac-conservancy-bethesda</t>
+  </si>
+  <si>
+    <t>Chief Financial and Operating Officer, Institute for Women's Policy Research</t>
+  </si>
+  <si>
+    <t>Institute for Women's Policy Research</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 196992.00 - 235980.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Women, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/6dea14a3f76a4677bdf942de2eef7e98-chief-financial-and-operating-officer-institute-for-womens-policy-research-institute-for-womens-policy-research-washington</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>Employment Horizons</t>
+  </si>
+  <si>
+    <t>Hanover, New Jersey</t>
+  </si>
+  <si>
+    <t>Disability, Job Workplace, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a7ddbef685246c48a6561cfb7dc8899-chief-financial-officer-employment-horizons-hanover</t>
+  </si>
+  <si>
+    <t>Chief Operating Oficer</t>
+  </si>
+  <si>
+    <t>Association for Middle Level Education</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/672e84d2aecb4aae8a36df01905082e2-chief-operating-oficer-association-for-middle-level-education-westerville</t>
+  </si>
+  <si>
+    <t>Chief Philanthropy Officer</t>
+  </si>
+  <si>
+    <t>American Prairie</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea86c83cc26f49f6be63b33180120104-chief-philanthropy-officer-american-prairie-bozeman</t>
+  </si>
+  <si>
+    <t>Community Growth Builder</t>
+  </si>
+  <si>
+    <t>Nextus</t>
+  </si>
+  <si>
+    <t>International Relations, Media, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99b5e904ac024792a6b04110586247e8-community-growth-builder-nextus-torornto</t>
+  </si>
+  <si>
+    <t>Comptroller</t>
+  </si>
+  <si>
+    <t>The Mount</t>
+  </si>
+  <si>
+    <t>Lenox, MA</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/69dc03bd1ab44ed29e341c7d68375593-comptroller-the-mount-lenox</t>
+  </si>
+  <si>
+    <t>Coordinador Zonal (Part Time) - Campaña Diálogo Directo</t>
+  </si>
+  <si>
+    <t>MÉDICOS SIN FRONTERAS LAT</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Health Medicine, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db0cfc49f05445af9127cb322417db75-coordinador-zonal-part-time-campana-dialogo-directo-medicos-sin-fronteras-lat-buenos-aires</t>
+  </si>
+  <si>
+    <t>Deputy Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Doctors Without Borders/Médecins Sans Frontières (MSF) - USA</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 173720.00 - 221492.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b2dce1a6f1c47a484c42361d9738866-deputy-chief-development-officer-doctors-without-bordersmedecins-sans-frontieres-msf-usa-new-york</t>
+  </si>
+  <si>
+    <t>Deputy Director, Financial Planning &amp; Analysis</t>
+  </si>
+  <si>
+    <t>Together for Girls</t>
+  </si>
+  <si>
+    <t>USD 97000.00 - 113000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5402dca4cd574815938209882d331f7f-deputy-director-financial-planning-analysis-together-for-girls-washington</t>
+  </si>
+  <si>
+    <t>Development Officer, Planned Giving</t>
+  </si>
+  <si>
+    <t>Mount Sinai Health System, New York</t>
+  </si>
+  <si>
+    <t>USD 68179.74 - 76960.02/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e667a18821d4af39af0ba24f32444e6-development-officer-planned-giving-mount-sinai-health-system-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Digital &amp; Systems Manager</t>
+  </si>
+  <si>
+    <t>A2 (Anthropocene Alliance)</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Disaster Relief</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60ab5f1d632c4dc8b4e95fc35bf45cc3-digital-systems-manager-a2-anthropocene-alliance-north-miami-beach</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>MetroSquash</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77e9916be5b9440a9ff8d253f11330b6-director-of-development-metrosquash-chicago</t>
+  </si>
+  <si>
+    <t>Director of Support and Education</t>
+  </si>
+  <si>
+    <t>Myelodysplastic Syndromes (MDS) Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39d063530f404518b0460e254edd27a6-director-of-support-and-education-myelodysplastic-syndromes-mds-foundation-inc-new-york</t>
+  </si>
+  <si>
+    <t>English Professor</t>
+  </si>
+  <si>
+    <t>SEEDS - Access Changes Everything</t>
+  </si>
+  <si>
+    <t>South Orange Village, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 240.00 - 240.00/day</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8ae07f13fdb94812bbf00be1067ccf9d-english-professor-seeds-access-changes-everything-south-orange-village</t>
+  </si>
+  <si>
+    <t>Events &amp; Marketing Manager</t>
+  </si>
+  <si>
+    <t>Hospice of Santa Barbara</t>
+  </si>
+  <si>
+    <t>Santa Barbara, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Mental Health, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4df16abe058d4b57adde0470d92ee81a-events-marketing-manager-hospice-of-santa-barbara-santa-barbara</t>
+  </si>
+  <si>
+    <t>Events and Ministry Coordinator (Multiple Locations &amp; Flexible Opportunities)</t>
+  </si>
+  <si>
+    <t>Apartment Life</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>USD 15.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a785e91f11fe4537a152a523153696c0-events-and-ministry-coordinator-multiple-locations-flexible-opportunities-apartment-life-dallas</t>
+  </si>
+  <si>
+    <t>Bellingham, Washington</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>Conservation Job Board</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b80c1b5e1c864f45bc7f924fc2a2224f-executive-director-wild-whatcom-bellingham</t>
+  </si>
+  <si>
+    <t>Executive Director (US-Based)</t>
+  </si>
+  <si>
+    <t>Rooted Wisdom Africa, Into Your Hands Africa</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74da214b38124170b4e9d5b6ca1d2f08-executive-director-us-based-rooted-wisdom-africa-into-your-hands-africa-denver</t>
+  </si>
+  <si>
+    <t>Facilitator, Public Service Leadership Institute</t>
+  </si>
+  <si>
+    <t>Partnership for Public Service</t>
+  </si>
+  <si>
+    <t>Policy, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a7bc377ae2444668df055737a7b6e27-facilitator-public-service-leadership-institute-partnership-for-public-service-washington</t>
+  </si>
+  <si>
+    <t>Facilities Director</t>
+  </si>
+  <si>
+    <t>Art Students League of New York</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21dd334b4833491bacc96e71e6eb7ad2-facilities-director-art-students-league-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Family Partner Behavioral Specialist</t>
+  </si>
+  <si>
+    <t>The Parents' Place of Maryland</t>
+  </si>
+  <si>
+    <t>Lusby, Maryland</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6922b1f4d3ed44f1b2399907e67e07f4-family-partner-behavioral-specialist-the-parents-place-of-maryland-lusby</t>
+  </si>
+  <si>
+    <t>Farmers' Market Manager</t>
+  </si>
+  <si>
+    <t>Urban Village Farmers' Market Association</t>
+  </si>
+  <si>
+    <t>San Carlos, California</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eeb42d44cce445d4bddff924336d4d60-farmers-market-manager-urban-village-farmers-market-association-san-carlos</t>
+  </si>
+  <si>
+    <t>Finance Associate (part-time)</t>
+  </si>
+  <si>
+    <t>ArtsConnection</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0c1e9faef75473cb4754d8d12041338-finance-associate-part-time-artsconnection-new-york</t>
+  </si>
+  <si>
+    <t>Geopolitics Researcher [Remote - Part Time]</t>
+  </si>
+  <si>
+    <t>Center for Asia-Pacific Strategy and Taiwan Studies</t>
+  </si>
+  <si>
+    <t>USD 300.00/month</t>
+  </si>
+  <si>
+    <t>International Relations, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f74b31992e1540888a4f231a87019b03-geopolitics-researcher-remote-part-time-center-for-asia-pacific-strategy-and-taiwan-studies-taipei</t>
+  </si>
+  <si>
+    <t>Gift Planning Advisor</t>
+  </si>
+  <si>
+    <t>Seattle Foundation</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 96000.00 - 104000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7cc5347d3f95491b9b63383cc7439b3b-gift-planning-advisor-seattle-foundation-seattle</t>
+  </si>
+  <si>
+    <t>National Association of Conservation Districts</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e09be5f615b743b79dd25ca9126815c0-grants-administrator-national-association-of-conservation-districts-washington</t>
+  </si>
+  <si>
     <t>Grants Manager &amp; Partnerships Coordinator</t>
   </si>
   <si>
@@ -49,16 +1132,589 @@
     <t>Krong Siem Reap, Siem Reap Province, KH</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Conflict Resolution</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/a5d398d4d31e432886bca73893bf1f1b-grants-manager-partnerships-coordinator-centre-for-peace-and-conflict-studies-krong-siem-reap</t>
+  </si>
+  <si>
+    <t>Graphic Designer</t>
+  </si>
+  <si>
+    <t>Kaufman Music Center</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9829534ec794cf6b4ba0126dc45018f-graphic-designer-kaufman-music-center-new-york</t>
+  </si>
+  <si>
+    <t>International Director</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/097d5aed0cf94c10b51925c5c98b21a8-international-director-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Junior Art Director</t>
+  </si>
+  <si>
+    <t>Americares</t>
+  </si>
+  <si>
+    <t>USD 69760.00 - 76600.00/year</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Health Medicine, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5209ab39d084e528e078ee43421072e-junior-art-director-americares-stamford</t>
+  </si>
+  <si>
+    <t>Lead Canvasser</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/44fa7be526a74407915463e997c463d6-lead-canvasser-new-economic-justice-organizing-project-new-orleans</t>
+  </si>
+  <si>
+    <t>Literacy Tutor (PT, Temporary)</t>
+  </si>
+  <si>
+    <t>Masa</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd8ccc2a101b40f28f8b2a407066f36a-literacy-tutor-pt-temporary-masa-bronx</t>
+  </si>
+  <si>
+    <t>Logistics and Supply Coordinator - HR Roster</t>
+  </si>
+  <si>
+    <t>INTERSOS</t>
+  </si>
+  <si>
+    <t>Rome, 62, IT</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>EUR 3690.00 - 4245.00/month</t>
+  </si>
+  <si>
+    <t>International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea272f18ee964bc7beddf2f60609537d-logistics-and-supply-coordinator-hr-roster-intersos-rome</t>
+  </si>
+  <si>
+    <t>Manager, Digital Platforms</t>
+  </si>
+  <si>
+    <t>New York City Ballet</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f82714edb74a41c6a705e3a9d265bdcb-manager-digital-platforms-new-york-city-ballet-new-york</t>
+  </si>
+  <si>
+    <t>Oceans Campaigner</t>
+  </si>
+  <si>
+    <t>Center for Biological Diversity</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20700ba39ad6410a888556d2d39b6974-oceans-campaigner-center-for-biological-diversity-oakland</t>
+  </si>
+  <si>
+    <t>Operations and Finance Manager</t>
+  </si>
+  <si>
+    <t>National Council for Occupational Safety and Health</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc84496d81db4374b043e98109cb66d1-operations-and-finance-manager-national-council-for-occupational-safety-and-health-austin</t>
+  </si>
+  <si>
+    <t>Operations Coordinator (30hr/week), Hybrid/Princeton, NJ</t>
+  </si>
+  <si>
+    <t>Young Audiences New Jersey &amp; Eastern Pennsylvania</t>
+  </si>
+  <si>
+    <t>Princeton, NJ</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 42000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/14b14f2837904958b1bd7bd9451c5e9a-operations-coordinator-30hrweek-hybridprinceton-nj-young-audiences-new-jersey-eastern-pennsylvania-princeton</t>
+  </si>
+  <si>
+    <t>Organizer</t>
+  </si>
+  <si>
+    <t>Youth Represent</t>
+  </si>
+  <si>
+    <t>USD 60683.00 - 66629.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/18440839e1754303a411879d4ea95052-organizer-youth-represent-new-york</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>USD 58350.00 - 66629.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e08be2854bd34ae7802edd341bc9172f-paralegal-youth-represent-new-york</t>
+  </si>
+  <si>
+    <t>Part-Time Journalist Support Correspondent</t>
+  </si>
+  <si>
+    <t>American Association for the Advancement of Science (AAAS)</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/278d6512d40d4e2d99646d71ba39da91-part-time-journalist-support-correspondent-american-association-for-the-advancement-of-science-aaas-washington</t>
+  </si>
+  <si>
+    <t>Part-Time Management Accountant</t>
+  </si>
+  <si>
+    <t>Accelerating Circularity Inc.</t>
+  </si>
+  <si>
+    <t>USD 550.00 - 550.00/day</t>
+  </si>
+  <si>
+    <t>Transparency Oversight, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc49385d870d48b99c26e593c7592877-part-time-management-accountant-accelerating-circularity-inc-middletown</t>
+  </si>
+  <si>
+    <t>People &amp; Culture Director</t>
+  </si>
+  <si>
+    <t>Center for the Art of Translation</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>USD 107000.00 - 107000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab613e51463045fe81bd263061788d4a-people-culture-director-center-for-the-art-of-translation-san-francisco</t>
+  </si>
+  <si>
+    <t>Permitting Policy Director</t>
+  </si>
+  <si>
+    <t>Permit Power</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd4c1e10028b435f97fc6319d1f3a66d-permitting-policy-director-permit-power-san-francisco</t>
+  </si>
+  <si>
+    <t>Play for P.I.N.K Associate, Fundraising Operations</t>
+  </si>
+  <si>
+    <t>The Breast Cancer Research Foundation</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Job Workplace, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92f2d8d6a241490f9002c479df933dae-play-for-pink-associate-fundraising-operations-the-breast-cancer-research-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Polycapital Academy Lead</t>
+  </si>
+  <si>
+    <t>Regeneration Group (Generation Pledge)</t>
+  </si>
+  <si>
+    <t>USD 88842.44/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7eec608aa9f44980bca6ff3f878fddf8-polycapital-academy-lead-regeneration-group-generation-pledge-millburn</t>
+  </si>
+  <si>
+    <t>Post-baccalaureate/Post-doctoral Bioethics Fellowship at the NIH</t>
+  </si>
+  <si>
+    <t>Department of Bioethics, Clinical Center, National Institutes of Health</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/2ccdec4c9b8440a48276f7770ad6c147-post-baccalaureatepost-doctoral-bioethics-fellowship-at-the-nih-department-of-bioethics-clinical-center-national-institutes-of-health-bethesda</t>
+  </si>
+  <si>
+    <t>Press Secretary and Media Relations Manager</t>
+  </si>
+  <si>
+    <t>Brady United Against Gun Violence</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49b17d6297484015aefcd9a116298e2b-press-secretary-and-media-relations-manager-brady-united-against-gun-violence-washington</t>
+  </si>
+  <si>
+    <t>Procurement Specialist</t>
+  </si>
+  <si>
+    <t>Animal Care Centers of NYC</t>
+  </si>
+  <si>
+    <t>USD 28.84 - 31.25/hour</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b21a4f174fe47e5af0ccbfd5711904a-procurement-specialist-animal-care-centers-of-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Program &amp; Family Services Coordinator (MSW)</t>
+  </si>
+  <si>
+    <t>Fred's Footsteps</t>
+  </si>
+  <si>
+    <t>Conshohocken, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be145f8874b74afabe82ac557d9f58ad-program-family-services-coordinator-msw-freds-footsteps-conshohocken</t>
+  </si>
+  <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>Science Club for Girls</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7729fa5fb9434c90b529b0d3ba2ccfcf-program-assistant-science-club-for-girls-cambridge</t>
+  </si>
+  <si>
+    <t>Program Associate, Climate</t>
+  </si>
+  <si>
+    <t>Barr Foundation</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/606b428c796d49e6aee1169268afac55-program-associate-climate-barr-foundation-boston</t>
+  </si>
+  <si>
+    <t>Program Director, Center for Talent Development</t>
+  </si>
+  <si>
+    <t>JCC Association</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37bb554b92ee456fa1a7c02f51a9feae-program-director-center-for-talent-development-jcc-association-new-york</t>
+  </si>
+  <si>
+    <t>Program Manager, JCC Maccabi</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/48224d9e06d14a788aaa78ef87eb67d0-program-manager-jcc-maccabi-jcc-association-kings-county</t>
+  </si>
+  <si>
+    <t>Public Benefits Staff Attorney</t>
+  </si>
+  <si>
+    <t>Montana Legal Services Association</t>
+  </si>
+  <si>
+    <t>Helena, Montana</t>
+  </si>
+  <si>
+    <t>USD 60500.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/919edc32ac344fe7936d9696812fc69e-public-benefits-staff-attorney-montana-legal-services-association-helena</t>
+  </si>
+  <si>
+    <t>Resident Services Coordinator</t>
+  </si>
+  <si>
+    <t>Native American Youth and Family Center (NAYA)</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/01b927f40d1a451586f996ecff257858-resident-services-coordinator-native-american-youth-and-family-center-naya-portland</t>
+  </si>
+  <si>
+    <t>Senior Counsel/Advisor</t>
+  </si>
+  <si>
+    <t>AFL-CIO Tech Institute</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/851e16c84993414981bc54c1cdb8c30e-senior-counseladvisor-afl-cio-tech-institute-washington</t>
+  </si>
+  <si>
+    <t>Senior Director, Foundation Relations</t>
+  </si>
+  <si>
+    <t>Alliance for Justice</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b8760473c9d4cfbbe7d4661f2b3f53f-senior-director-foundation-relations-alliance-for-justice-washington</t>
+  </si>
+  <si>
+    <t>Senior Foundation Relations Manager</t>
+  </si>
+  <si>
+    <t>USD 93425.00 - 103582.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc360ac9e0a24d45a4fab94566e07f3d-senior-foundation-relations-manager-alliance-for-justice-washington</t>
+  </si>
+  <si>
+    <t>Senior Managing Director of Organizing</t>
+  </si>
+  <si>
+    <t>The Chisholm Legacy Project: A Resource Hub for Black Frontline Climate Justice Leadership</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8ab38ef87a54be8b237024768e48768-senior-managing-director-of-organizing-the-chisholm-legacy-project-a-resource-hub-for-black-frontline-climate-justice-leadership-burtonsville</t>
+  </si>
+  <si>
+    <t>Social Media and Community Manager</t>
+  </si>
+  <si>
+    <t>American College of Gastroenterology</t>
+  </si>
+  <si>
+    <t>North Bethesda, Maryland</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Science Technology, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e59dfb1e52e341a8b2335cea5dd5e628-social-media-and-community-manager-american-college-of-gastroenterology-north-bethesda</t>
+  </si>
+  <si>
+    <t>Social Work Lead / Manager</t>
+  </si>
+  <si>
+    <t>VAST BC - Vancouver Association for Survivors of Torture</t>
+  </si>
+  <si>
+    <t>Vancouver, British Columbia, CA</t>
+  </si>
+  <si>
+    <t>CAD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5887f2775a6844d9b33fa40c83c8abed-social-work-lead-manager-vast-bc-vancouver-association-for-survivors-of-torture-vancouver</t>
+  </si>
+  <si>
+    <t>Surrey, British Columbia, CA</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ac90fa698314e7cb8435ae512e52ac6-social-work-lead-manager-vast-bc-vancouver-association-for-survivors-of-torture-surrey</t>
+  </si>
+  <si>
+    <t>Social Worker</t>
+  </si>
+  <si>
+    <t>Town of Ashland - Department of Prevention &amp; Human Services</t>
+  </si>
+  <si>
+    <t>Ashland, Massachusetts</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/b2d99d7a43264212b3254fe6fc12c0aa-social-worker-town-of-ashland-department-of-prevention-human-services-ashland</t>
+  </si>
+  <si>
+    <t>Staff Assistant</t>
+  </si>
+  <si>
+    <t>Office of Senator Peter Welch</t>
+  </si>
+  <si>
+    <t>Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/a39760369e944cadacdaf312dbb6b6ad-staff-assistant-office-of-senator-peter-welch-burlington</t>
+  </si>
+  <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>UnLocal, Inc.</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7474f682b41421abb6f82c8353c74f2-supervising-attorney-unlocal-inc-new-york</t>
+  </si>
+  <si>
+    <t>Technical Support Specialist</t>
+  </si>
+  <si>
+    <t>Civilization Research Institute</t>
+  </si>
+  <si>
+    <t>Asheville, North Carolina</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9564fc725d842969eb49aef7964f913-technical-support-specialist-civilization-research-institute-asheville</t>
+  </si>
+  <si>
+    <t>Vice President, Advancement and Philanthropic Engagement, Institute for Women's Policy Research</t>
+  </si>
+  <si>
+    <t>USD 156978.00 - 192586.00/year</t>
+  </si>
+  <si>
+    <t>Women, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f5d68abac8bf4a5992fa10d2bfe0071a-vice-president-advancement-and-philanthropic-engagement-institute-for-womens-policy-research-institute-for-womens-policy-research-washington</t>
   </si>
 </sst>
 </file>
@@ -444,7 +2100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -483,8 +2139,709 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
+        <v>125</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" t="s">
+        <v>138</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>143</v>
+      </c>
+      <c r="F27" t="s">
+        <v>144</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" t="s">
+        <v>151</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -540,7 +2897,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -581,31 +2938,1954 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>168</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" t="s">
+        <v>169</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" t="s">
+        <v>194</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F9" t="s">
+        <v>204</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" t="s">
+        <v>213</v>
+      </c>
+      <c r="F11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" t="s">
+        <v>217</v>
+      </c>
+      <c r="F12" t="s">
+        <v>218</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" t="s">
+        <v>221</v>
+      </c>
+      <c r="F13" t="s">
+        <v>218</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" t="s">
+        <v>226</v>
+      </c>
+      <c r="E14" t="s">
+        <v>227</v>
+      </c>
+      <c r="F14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E15" t="s">
+        <v>233</v>
+      </c>
+      <c r="F15" t="s">
+        <v>234</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D16" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" t="s">
+        <v>239</v>
+      </c>
+      <c r="F16" t="s">
+        <v>240</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>242</v>
+      </c>
+      <c r="B17" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" t="s">
+        <v>244</v>
+      </c>
+      <c r="D17" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F17" t="s">
+        <v>245</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B18" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E18" t="s">
+        <v>249</v>
+      </c>
+      <c r="F18" t="s">
+        <v>250</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>252</v>
+      </c>
+      <c r="B19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" t="s">
+        <v>177</v>
+      </c>
+      <c r="E19" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" t="s">
+        <v>255</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>257</v>
+      </c>
+      <c r="B20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C20" t="s">
+        <v>176</v>
+      </c>
+      <c r="D20" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" t="s">
+        <v>259</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>261</v>
+      </c>
+      <c r="B21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C21" t="s">
+        <v>263</v>
+      </c>
+      <c r="D21" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" t="s">
+        <v>264</v>
+      </c>
+      <c r="F21" t="s">
+        <v>194</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>266</v>
+      </c>
+      <c r="B22" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" t="s">
+        <v>268</v>
+      </c>
+      <c r="D22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" t="s">
+        <v>169</v>
+      </c>
+      <c r="F22" t="s">
+        <v>269</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>271</v>
+      </c>
+      <c r="B23" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" t="s">
+        <v>273</v>
+      </c>
+      <c r="D23" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" t="s">
+        <v>274</v>
+      </c>
+      <c r="F23" t="s">
+        <v>169</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>276</v>
+      </c>
+      <c r="B24" t="s">
+        <v>277</v>
+      </c>
+      <c r="C24" t="s">
+        <v>176</v>
+      </c>
+      <c r="D24" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" t="s">
+        <v>278</v>
+      </c>
+      <c r="F24" t="s">
+        <v>279</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B25" t="s">
+        <v>282</v>
+      </c>
+      <c r="C25" t="s">
+        <v>273</v>
+      </c>
+      <c r="D25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" t="s">
+        <v>283</v>
+      </c>
+      <c r="F25" t="s">
+        <v>284</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>286</v>
+      </c>
+      <c r="B26" t="s">
+        <v>287</v>
+      </c>
+      <c r="C26" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" t="s">
+        <v>169</v>
+      </c>
+      <c r="F26" t="s">
+        <v>288</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>290</v>
+      </c>
+      <c r="B27" t="s">
+        <v>291</v>
+      </c>
+      <c r="C27" t="s">
+        <v>292</v>
+      </c>
+      <c r="D27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" t="s">
+        <v>293</v>
+      </c>
+      <c r="F27" t="s">
+        <v>294</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B28" t="s">
+        <v>297</v>
+      </c>
+      <c r="C28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" t="s">
+        <v>177</v>
+      </c>
+      <c r="E28" t="s">
+        <v>298</v>
+      </c>
+      <c r="F28" t="s">
+        <v>299</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>301</v>
+      </c>
+      <c r="B29" t="s">
+        <v>302</v>
+      </c>
+      <c r="C29" t="s">
+        <v>303</v>
+      </c>
+      <c r="D29" t="s">
+        <v>226</v>
+      </c>
+      <c r="E29" t="s">
+        <v>304</v>
+      </c>
+      <c r="F29" t="s">
+        <v>305</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>307</v>
+      </c>
+      <c r="B30" t="s">
+        <v>308</v>
+      </c>
+      <c r="C30" t="s">
+        <v>309</v>
+      </c>
+      <c r="D30" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" t="s">
+        <v>310</v>
+      </c>
+      <c r="F30" t="s">
+        <v>311</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>313</v>
+      </c>
+      <c r="B31" t="s">
+        <v>314</v>
+      </c>
+      <c r="C31" t="s">
+        <v>315</v>
+      </c>
+      <c r="D31" t="s">
+        <v>177</v>
+      </c>
+      <c r="E31" t="s">
+        <v>316</v>
+      </c>
+      <c r="F31" t="s">
+        <v>317</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" t="s">
+        <v>319</v>
+      </c>
+      <c r="D32" t="s">
+        <v>177</v>
+      </c>
+      <c r="E32" t="s">
+        <v>320</v>
+      </c>
+      <c r="F32" t="s">
+        <v>321</v>
+      </c>
+      <c r="G32" t="s">
+        <v>322</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>324</v>
+      </c>
+      <c r="B33" t="s">
+        <v>325</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" t="s">
+        <v>326</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>328</v>
+      </c>
+      <c r="B34" t="s">
+        <v>329</v>
+      </c>
+      <c r="C34" t="s">
+        <v>238</v>
+      </c>
+      <c r="D34" t="s">
+        <v>177</v>
+      </c>
+      <c r="E34" t="s">
+        <v>310</v>
+      </c>
+      <c r="F34" t="s">
+        <v>330</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>332</v>
+      </c>
+      <c r="B35" t="s">
+        <v>333</v>
+      </c>
+      <c r="C35" t="s">
+        <v>334</v>
+      </c>
+      <c r="D35" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35" t="s">
+        <v>335</v>
+      </c>
+      <c r="F35" t="s">
+        <v>336</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>338</v>
+      </c>
+      <c r="B36" t="s">
+        <v>339</v>
+      </c>
+      <c r="C36" t="s">
+        <v>340</v>
+      </c>
+      <c r="D36" t="s">
+        <v>177</v>
+      </c>
+      <c r="E36" t="s">
+        <v>341</v>
+      </c>
+      <c r="F36" t="s">
+        <v>342</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>344</v>
+      </c>
+      <c r="B37" t="s">
+        <v>345</v>
+      </c>
+      <c r="C37" t="s">
+        <v>346</v>
+      </c>
+      <c r="D37" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" t="s">
+        <v>347</v>
+      </c>
+      <c r="F37" t="s">
+        <v>348</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>350</v>
+      </c>
+      <c r="B38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C38" t="s">
+        <v>273</v>
+      </c>
+      <c r="D38" t="s">
+        <v>167</v>
+      </c>
+      <c r="E38" t="s">
+        <v>352</v>
+      </c>
+      <c r="F38" t="s">
+        <v>353</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>355</v>
+      </c>
+      <c r="B39" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" t="s">
+        <v>176</v>
+      </c>
+      <c r="D39" t="s">
+        <v>167</v>
+      </c>
+      <c r="E39" t="s">
+        <v>357</v>
+      </c>
+      <c r="F39" t="s">
+        <v>358</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>360</v>
+      </c>
+      <c r="B40" t="s">
+        <v>361</v>
+      </c>
+      <c r="C40" t="s">
+        <v>362</v>
+      </c>
+      <c r="D40" t="s">
+        <v>177</v>
+      </c>
+      <c r="E40" t="s">
+        <v>363</v>
+      </c>
+      <c r="F40" t="s">
+        <v>364</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" t="s">
+        <v>366</v>
+      </c>
+      <c r="C41" t="s">
+        <v>176</v>
+      </c>
+      <c r="D41" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" t="s">
+        <v>367</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>369</v>
+      </c>
+      <c r="B42" t="s">
+        <v>370</v>
+      </c>
+      <c r="C42" t="s">
+        <v>371</v>
+      </c>
+      <c r="D42" t="s">
+        <v>177</v>
+      </c>
+      <c r="E42" t="s">
+        <v>169</v>
+      </c>
+      <c r="F42" t="s">
+        <v>372</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>374</v>
+      </c>
+      <c r="B43" t="s">
+        <v>375</v>
+      </c>
+      <c r="C43" t="s">
+        <v>273</v>
+      </c>
+      <c r="D43" t="s">
+        <v>177</v>
+      </c>
+      <c r="E43" t="s">
+        <v>376</v>
+      </c>
+      <c r="F43" t="s">
+        <v>353</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>378</v>
+      </c>
+      <c r="B44" t="s">
+        <v>379</v>
+      </c>
+      <c r="C44" t="s">
+        <v>176</v>
+      </c>
+      <c r="D44" t="s">
+        <v>380</v>
+      </c>
+      <c r="E44" t="s">
+        <v>381</v>
+      </c>
+      <c r="F44" t="s">
+        <v>382</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>384</v>
+      </c>
+      <c r="B45" t="s">
+        <v>385</v>
+      </c>
+      <c r="C45" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" t="s">
+        <v>177</v>
+      </c>
+      <c r="E45" t="s">
+        <v>386</v>
+      </c>
+      <c r="F45" t="s">
+        <v>387</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>389</v>
+      </c>
+      <c r="B46" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" t="s">
+        <v>225</v>
+      </c>
+      <c r="D46" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" t="s">
+        <v>390</v>
+      </c>
+      <c r="F46" t="s">
+        <v>228</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>392</v>
+      </c>
+      <c r="B47" t="s">
+        <v>393</v>
+      </c>
+      <c r="C47" t="s">
+        <v>394</v>
+      </c>
+      <c r="D47" t="s">
+        <v>226</v>
+      </c>
+      <c r="E47" t="s">
+        <v>395</v>
+      </c>
+      <c r="F47" t="s">
+        <v>396</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>398</v>
+      </c>
+      <c r="B48" t="s">
+        <v>399</v>
+      </c>
+      <c r="C48" t="s">
+        <v>400</v>
+      </c>
+      <c r="D48" t="s">
+        <v>401</v>
+      </c>
+      <c r="E48" t="s">
+        <v>402</v>
+      </c>
+      <c r="F48" t="s">
+        <v>403</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>405</v>
+      </c>
+      <c r="B49" t="s">
+        <v>406</v>
+      </c>
+      <c r="C49" t="s">
+        <v>334</v>
+      </c>
+      <c r="D49" t="s">
+        <v>177</v>
+      </c>
+      <c r="E49" t="s">
+        <v>407</v>
+      </c>
+      <c r="F49" t="s">
+        <v>408</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>410</v>
+      </c>
+      <c r="B50" t="s">
+        <v>411</v>
+      </c>
+      <c r="C50" t="s">
+        <v>176</v>
+      </c>
+      <c r="D50" t="s">
+        <v>177</v>
+      </c>
+      <c r="E50" t="s">
+        <v>412</v>
+      </c>
+      <c r="F50" t="s">
+        <v>413</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>415</v>
+      </c>
+      <c r="B51" t="s">
+        <v>416</v>
+      </c>
+      <c r="C51" t="s">
+        <v>176</v>
+      </c>
+      <c r="D51" t="s">
+        <v>177</v>
+      </c>
+      <c r="E51" t="s">
+        <v>264</v>
+      </c>
+      <c r="F51" t="s">
+        <v>417</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>419</v>
+      </c>
+      <c r="B52" t="s">
+        <v>420</v>
+      </c>
+      <c r="C52" t="s">
+        <v>421</v>
+      </c>
+      <c r="D52" t="s">
+        <v>177</v>
+      </c>
+      <c r="E52" t="s">
+        <v>422</v>
+      </c>
+      <c r="F52" t="s">
+        <v>353</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>424</v>
+      </c>
+      <c r="B53" t="s">
+        <v>425</v>
+      </c>
+      <c r="C53" t="s">
+        <v>273</v>
+      </c>
+      <c r="D53" t="s">
+        <v>177</v>
+      </c>
+      <c r="E53" t="s">
+        <v>426</v>
+      </c>
+      <c r="F53" t="s">
+        <v>427</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>429</v>
+      </c>
+      <c r="B54" t="s">
+        <v>425</v>
+      </c>
+      <c r="C54" t="s">
+        <v>273</v>
+      </c>
+      <c r="D54" t="s">
+        <v>177</v>
+      </c>
+      <c r="E54" t="s">
+        <v>430</v>
+      </c>
+      <c r="F54" t="s">
+        <v>427</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>432</v>
+      </c>
+      <c r="B55" t="s">
+        <v>433</v>
+      </c>
+      <c r="C55" t="s">
+        <v>176</v>
+      </c>
+      <c r="D55" t="s">
+        <v>226</v>
+      </c>
+      <c r="E55" t="s">
+        <v>434</v>
+      </c>
+      <c r="F55" t="s">
+        <v>435</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>437</v>
+      </c>
+      <c r="B56" t="s">
+        <v>438</v>
+      </c>
+      <c r="C56" t="s">
+        <v>176</v>
+      </c>
+      <c r="D56" t="s">
+        <v>167</v>
+      </c>
+      <c r="E56" t="s">
+        <v>439</v>
+      </c>
+      <c r="F56" t="s">
+        <v>440</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>442</v>
+      </c>
+      <c r="B57" t="s">
+        <v>443</v>
+      </c>
+      <c r="C57" t="s">
+        <v>444</v>
+      </c>
+      <c r="D57" t="s">
+        <v>177</v>
+      </c>
+      <c r="E57" t="s">
+        <v>445</v>
+      </c>
+      <c r="F57" t="s">
+        <v>336</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>447</v>
+      </c>
+      <c r="B58" t="s">
+        <v>448</v>
+      </c>
+      <c r="C58" t="s">
+        <v>176</v>
+      </c>
+      <c r="D58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" t="s">
+        <v>449</v>
+      </c>
+      <c r="F58" t="s">
+        <v>450</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>452</v>
+      </c>
+      <c r="B59" t="s">
+        <v>453</v>
+      </c>
+      <c r="C59" t="s">
+        <v>273</v>
+      </c>
+      <c r="D59" t="s">
+        <v>177</v>
+      </c>
+      <c r="E59" t="s">
+        <v>454</v>
+      </c>
+      <c r="F59" t="s">
+        <v>455</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>457</v>
+      </c>
+      <c r="B60" t="s">
+        <v>458</v>
+      </c>
+      <c r="C60" t="s">
+        <v>176</v>
+      </c>
+      <c r="D60" t="s">
+        <v>380</v>
+      </c>
+      <c r="E60" t="s">
+        <v>459</v>
+      </c>
+      <c r="F60" t="s">
+        <v>460</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>462</v>
+      </c>
+      <c r="B61" t="s">
+        <v>463</v>
+      </c>
+      <c r="C61" t="s">
+        <v>232</v>
+      </c>
+      <c r="D61" t="s">
+        <v>401</v>
+      </c>
+      <c r="E61" t="s">
+        <v>169</v>
+      </c>
+      <c r="F61" t="s">
+        <v>464</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>466</v>
+      </c>
+      <c r="B62" t="s">
+        <v>467</v>
+      </c>
+      <c r="C62" t="s">
+        <v>238</v>
+      </c>
+      <c r="D62" t="s">
+        <v>177</v>
+      </c>
+      <c r="E62" t="s">
+        <v>468</v>
+      </c>
+      <c r="F62" t="s">
+        <v>469</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>471</v>
+      </c>
+      <c r="B63" t="s">
+        <v>472</v>
+      </c>
+      <c r="C63" t="s">
+        <v>273</v>
+      </c>
+      <c r="D63" t="s">
+        <v>177</v>
+      </c>
+      <c r="E63" t="s">
+        <v>473</v>
+      </c>
+      <c r="F63" t="s">
+        <v>474</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>476</v>
+      </c>
+      <c r="B64" t="s">
+        <v>477</v>
+      </c>
+      <c r="C64" t="s">
+        <v>478</v>
+      </c>
+      <c r="D64" t="s">
+        <v>177</v>
+      </c>
+      <c r="E64" t="s">
+        <v>479</v>
+      </c>
+      <c r="F64" t="s">
+        <v>480</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>482</v>
+      </c>
+      <c r="B65" t="s">
+        <v>483</v>
+      </c>
+      <c r="C65" t="s">
+        <v>484</v>
+      </c>
+      <c r="D65" t="s">
+        <v>177</v>
+      </c>
+      <c r="E65" t="s">
+        <v>485</v>
+      </c>
+      <c r="F65" t="s">
+        <v>486</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>488</v>
+      </c>
+      <c r="B66" t="s">
+        <v>489</v>
+      </c>
+      <c r="C66" t="s">
+        <v>198</v>
+      </c>
+      <c r="D66" t="s">
+        <v>177</v>
+      </c>
+      <c r="E66" t="s">
+        <v>490</v>
+      </c>
+      <c r="F66" t="s">
+        <v>234</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>492</v>
+      </c>
+      <c r="B67" t="s">
+        <v>493</v>
+      </c>
+      <c r="C67" t="s">
+        <v>273</v>
+      </c>
+      <c r="D67" t="s">
+        <v>177</v>
+      </c>
+      <c r="E67" t="s">
+        <v>494</v>
+      </c>
+      <c r="F67" t="s">
+        <v>495</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>497</v>
+      </c>
+      <c r="B68" t="s">
+        <v>493</v>
+      </c>
+      <c r="C68" t="s">
+        <v>498</v>
+      </c>
+      <c r="D68" t="s">
+        <v>177</v>
+      </c>
+      <c r="E68" t="s">
+        <v>203</v>
+      </c>
+      <c r="F68" t="s">
+        <v>499</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>501</v>
+      </c>
+      <c r="B69" t="s">
+        <v>502</v>
+      </c>
+      <c r="C69" t="s">
+        <v>503</v>
+      </c>
+      <c r="D69" t="s">
+        <v>177</v>
+      </c>
+      <c r="E69" t="s">
+        <v>504</v>
+      </c>
+      <c r="F69" t="s">
+        <v>505</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>507</v>
+      </c>
+      <c r="B70" t="s">
+        <v>508</v>
+      </c>
+      <c r="C70" t="s">
+        <v>509</v>
+      </c>
+      <c r="D70" t="s">
+        <v>177</v>
+      </c>
+      <c r="E70" t="s">
+        <v>510</v>
+      </c>
+      <c r="F70" t="s">
+        <v>511</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>513</v>
+      </c>
+      <c r="B71" t="s">
+        <v>514</v>
+      </c>
+      <c r="C71" t="s">
+        <v>238</v>
+      </c>
+      <c r="D71" t="s">
+        <v>177</v>
+      </c>
+      <c r="E71" t="s">
+        <v>515</v>
+      </c>
+      <c r="F71" t="s">
+        <v>228</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>517</v>
+      </c>
+      <c r="B72" t="s">
+        <v>518</v>
+      </c>
+      <c r="C72" t="s">
+        <v>176</v>
+      </c>
+      <c r="D72" t="s">
+        <v>177</v>
+      </c>
+      <c r="E72" t="s">
+        <v>519</v>
+      </c>
+      <c r="F72" t="s">
+        <v>520</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>522</v>
+      </c>
+      <c r="B73" t="s">
+        <v>518</v>
+      </c>
+      <c r="C73" t="s">
+        <v>176</v>
+      </c>
+      <c r="D73" t="s">
+        <v>177</v>
+      </c>
+      <c r="E73" t="s">
+        <v>523</v>
+      </c>
+      <c r="F73" t="s">
+        <v>520</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>525</v>
+      </c>
+      <c r="B74" t="s">
+        <v>526</v>
+      </c>
+      <c r="C74" t="s">
+        <v>176</v>
+      </c>
+      <c r="D74" t="s">
+        <v>177</v>
+      </c>
+      <c r="E74" t="s">
+        <v>249</v>
+      </c>
+      <c r="F74" t="s">
+        <v>527</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>529</v>
+      </c>
+      <c r="B75" t="s">
+        <v>530</v>
+      </c>
+      <c r="C75" t="s">
+        <v>531</v>
+      </c>
+      <c r="D75" t="s">
+        <v>177</v>
+      </c>
+      <c r="E75" t="s">
+        <v>532</v>
+      </c>
+      <c r="F75" t="s">
+        <v>533</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>535</v>
+      </c>
+      <c r="B76" t="s">
+        <v>536</v>
+      </c>
+      <c r="C76" t="s">
+        <v>537</v>
+      </c>
+      <c r="D76" t="s">
+        <v>177</v>
+      </c>
+      <c r="E76" t="s">
+        <v>538</v>
+      </c>
+      <c r="F76" t="s">
+        <v>539</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>535</v>
+      </c>
+      <c r="B77" t="s">
+        <v>536</v>
+      </c>
+      <c r="C77" t="s">
+        <v>541</v>
+      </c>
+      <c r="D77" t="s">
+        <v>177</v>
+      </c>
+      <c r="E77" t="s">
+        <v>538</v>
+      </c>
+      <c r="F77" t="s">
+        <v>539</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>543</v>
+      </c>
+      <c r="B78" t="s">
+        <v>544</v>
+      </c>
+      <c r="C78" t="s">
+        <v>545</v>
+      </c>
+      <c r="D78" t="s">
+        <v>177</v>
+      </c>
+      <c r="E78" t="s">
+        <v>203</v>
+      </c>
+      <c r="F78" t="s">
+        <v>546</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>548</v>
+      </c>
+      <c r="B79" t="s">
+        <v>549</v>
+      </c>
+      <c r="C79" t="s">
+        <v>550</v>
+      </c>
+      <c r="D79" t="s">
+        <v>177</v>
+      </c>
+      <c r="E79" t="s">
+        <v>551</v>
+      </c>
+      <c r="F79" t="s">
+        <v>552</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>554</v>
+      </c>
+      <c r="B80" t="s">
+        <v>555</v>
+      </c>
+      <c r="C80" t="s">
+        <v>273</v>
+      </c>
+      <c r="D80" t="s">
+        <v>177</v>
+      </c>
+      <c r="E80" t="s">
+        <v>556</v>
+      </c>
+      <c r="F80" t="s">
+        <v>218</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>558</v>
+      </c>
+      <c r="B81" t="s">
+        <v>559</v>
+      </c>
+      <c r="C81" t="s">
+        <v>560</v>
+      </c>
+      <c r="D81" t="s">
+        <v>177</v>
+      </c>
+      <c r="E81" t="s">
+        <v>169</v>
+      </c>
+      <c r="F81" t="s">
+        <v>561</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>563</v>
+      </c>
+      <c r="B82" t="s">
+        <v>237</v>
+      </c>
+      <c r="C82" t="s">
+        <v>238</v>
+      </c>
+      <c r="D82" t="s">
+        <v>177</v>
+      </c>
+      <c r="E82" t="s">
+        <v>564</v>
+      </c>
+      <c r="F82" t="s">
+        <v>565</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-10.xlsx
+++ b/docs/xlsx/jobs-2026-09-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="896">
   <si>
     <t>Title</t>
   </si>
@@ -508,6 +508,27 @@
     <t>https://www.conservationjobboard.com/job-listing-vice-president-of-community-engagement-denver-colorado/5461863635</t>
   </si>
   <si>
+    <t>Summer 2027 Legal Clerk</t>
+  </si>
+  <si>
+    <t>The Wilderness Society</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t>Less than 20,000</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/summer-2027-legal-clerk/</t>
+  </si>
+  <si>
     <t>Academic Group Leader</t>
   </si>
   <si>
@@ -544,9 +565,6 @@
     <t>Accelerate Change</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Full Time</t>
   </si>
   <si>
@@ -604,6 +622,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/73027f136b7c4f2a8ed0dbbf193bf010-admissions-director-macdowell-peterborough</t>
   </si>
   <si>
+    <t>Afterschool Coordinator (Castle Hill YMCA)</t>
+  </si>
+  <si>
+    <t>YMCA of Greater New York</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f8d865aaa8b047328fd14aa0cf45225f-afterschool-coordinator-castle-hill-ymca-ymca-of-greater-new-york-bronx-county</t>
+  </si>
+  <si>
     <t>Assistant Attorney General- Counsel II</t>
   </si>
   <si>
@@ -616,6 +652,24 @@
     <t>https://www.idealist.org/en/government-job/69ba2f3c108b4d6a86962af54c9741e8-assistant-attorney-general-counsel-ii-office-of-the-massachusetts-attorney-general-boston</t>
   </si>
   <si>
+    <t>Assistant Director of Data Systems &amp; Solutions</t>
+  </si>
+  <si>
+    <t>The Door - A Center of Alternatives</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 83000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d424378d69d4e7a8bd5551d6502f8d2-assistant-director-of-data-systems-solutions-the-door-a-center-of-alternatives-new-york</t>
+  </si>
+  <si>
     <t>Assistant Director, Events South Florida (preferably in Broward, Dade or South Palm Beach)</t>
   </si>
   <si>
@@ -634,6 +688,90 @@
     <t>https://www.idealist.org/en/nonprofit-job/7fb9431a08084deda21d75452a78e31f-assistant-director-events-south-florida-preferably-in-broward-dade-or-south-palm-beach-ajc-palm-beach</t>
   </si>
   <si>
+    <t>Assistant Director, Events South Florida (preferably in Miami Dade, Broward, or South Palm Beach)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7fb9431a08084deda21d75452a78e31f-assistant-director-events-south-florida-preferably-in-miami-dade-broward-or-south-palm-beach-ajc-palm-beach</t>
+  </si>
+  <si>
+    <t>Associate Attorney, Northwest Regional Office</t>
+  </si>
+  <si>
+    <t>Earthjustice</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 108200.00 - 134800.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/d2cf3020c0044ff4885e1ee7905a652e-associate-attorney-northwest-regional-office-earthjustice-seattle</t>
+  </si>
+  <si>
+    <t>Associate Community Organizer</t>
+  </si>
+  <si>
+    <t>Direct Action &amp; Research Training Center</t>
+  </si>
+  <si>
+    <t>Columbus, Ohio</t>
+  </si>
+  <si>
+    <t>USD 52000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9d3cb58de7b4513a3a075cc7647e761-associate-community-organizer-direct-action-research-training-center-columbus</t>
+  </si>
+  <si>
+    <t>Wichita, Kansas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7137a5bafe14b0897baf9ef8e200ea0-associate-community-organizer-direct-action-research-training-center-wichita</t>
+  </si>
+  <si>
+    <t>Tampa, Florida</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45783c43954f4421b50c3cba9a08b6b6-associate-community-organizer-direct-action-research-training-center-tampa</t>
+  </si>
+  <si>
+    <t>Associate Director of Early Literacy &amp; Instructional Partnerships</t>
+  </si>
+  <si>
+    <t>Literacy Inc. (LINC)</t>
+  </si>
+  <si>
+    <t>washington heights, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dec297d3db7f49058284d9603f7a8d16-associate-director-of-early-literacy-instructional-partnerships-literacy-inc-linc-washington-heights</t>
+  </si>
+  <si>
+    <t>Associate Teacher Twos and Threes (Early Childhood)</t>
+  </si>
+  <si>
+    <t>Central Synagogue</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c275c3a0b33e4fc78cb6a8985897c999-associate-teacher-twos-and-threes-early-childhood-central-synagogue-new-york</t>
+  </si>
+  <si>
     <t>Billing &amp; Legal Assistant (full-time) at Law Firm Exclusively Serving Nonproﬁt/Tax-Exempt Organizations</t>
   </si>
   <si>
@@ -661,6 +799,33 @@
     <t>https://www.idealist.org/en/consultant-job/631d92e2678a452d86418f62a5c08a54-billing-assistant-part-time-at-law-firm-exclusively-serving-nonprofittax-exempt-organizations-cheshire-law-group-philadelphia</t>
   </si>
   <si>
+    <t>Boat Building Teacher</t>
+  </si>
+  <si>
+    <t>TSNE</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62c093b708a3429b902bc1826bdea405-boat-building-teacher-tsne-boston</t>
+  </si>
+  <si>
+    <t>Boston Teacher Resident</t>
+  </si>
+  <si>
+    <t>Boston Plan for Excellence</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 20400.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca00b10fd31349dfbd0b38f99aaaa521-boston-teacher-resident-boston-plan-for-excellence-boston</t>
+  </si>
+  <si>
     <t>Business Engagement Director</t>
   </si>
   <si>
@@ -787,6 +952,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/ea86c83cc26f49f6be63b33180120104-chief-philanthropy-officer-american-prairie-bozeman</t>
   </si>
   <si>
+    <t>Client Services Associate</t>
+  </si>
+  <si>
+    <t>Roundabout Theatre Company</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64bbaff92b92435289583aadd69eedf0-client-services-associate-roundabout-theatre-company-new-york</t>
+  </si>
+  <si>
+    <t>Community Based Mentoring Program - Enrollment &amp; Match Specialist</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters of Greater Los Angeles</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4a5e4eb7364048a0a1445d9406e96836-community-based-mentoring-program-enrollment-match-specialist-big-brothers-big-sisters-of-greater-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Community Growth Builder</t>
   </si>
   <si>
@@ -829,15 +1021,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/db0cfc49f05445af9127cb322417db75-coordinador-zonal-part-time-campana-dialogo-directo-medicos-sin-fronteras-lat-buenos-aires</t>
   </si>
   <si>
+    <t>Counselling Course Designer</t>
+  </si>
+  <si>
+    <t>Onja</t>
+  </si>
+  <si>
+    <t>Toamasina, Atsinanana, MG</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43d0842c350c46998bf795fd832cc9a4-counselling-course-designer-onja-toamasina</t>
+  </si>
+  <si>
+    <t>Counsellor</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4dda41f4cf7940cfba0cf00e8915fa8a-counsellor-onja-toamasina</t>
+  </si>
+  <si>
     <t>Deputy Chief Development Officer</t>
   </si>
   <si>
     <t>Doctors Without Borders/Médecins Sans Frontières (MSF) - USA</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 173720.00 - 221492.00/year</t>
   </si>
   <si>
@@ -853,12 +1060,27 @@
     <t>USD 97000.00 - 113000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5402dca4cd574815938209882d331f7f-deputy-director-financial-planning-analysis-together-for-girls-washington</t>
   </si>
   <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Chesapeake Legal Alliance</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d4bef8a917c245ab98a3b4345c7a0811-development-coordinator-chesapeake-legal-alliance-annapolis</t>
+  </si>
+  <si>
     <t>Development Officer, Planned Giving</t>
   </si>
   <si>
@@ -886,6 +1108,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/60ab5f1d632c4dc8b4e95fc35bf45cc3-digital-systems-manager-a2-anthropocene-alliance-north-miami-beach</t>
   </si>
   <si>
+    <t>Directing Attorney – Access to Legal Justice Initiatives (Hybrid)</t>
+  </si>
+  <si>
+    <t>Community Legal Aid So Cal</t>
+  </si>
+  <si>
+    <t>Santa Ana, California</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96d4ab51e21c46b0aa4b20686f9c9b58-directing-attorney-access-to-legal-justice-initiatives-hybrid-community-legal-aid-so-cal-santa-ana</t>
+  </si>
+  <si>
+    <t>Directing Attorney – Compliance Grants &amp; Systems (Hybrid)</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a21b3c240e84906b28b94afeae0f5b3-directing-attorney-compliance-grants-systems-hybrid-community-legal-aid-so-cal-santa-ana</t>
+  </si>
+  <si>
+    <t>Director of Clinical Operations</t>
+  </si>
+  <si>
+    <t>Plan A Health, Inc</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Reproductive Health Rights, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0f6dc81e2764c0e99dcb9b531722f05-director-of-clinical-operations-plan-a-health-inc-louise</t>
+  </si>
+  <si>
     <t>Director of Development</t>
   </si>
   <si>
@@ -898,12 +1159,117 @@
     <t>USD 125000.00 - 150000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Education, Family</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/77e9916be5b9440a9ff8d253f11330b6-director-of-development-metrosquash-chicago</t>
   </si>
   <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>The Chisholm Legacy Project: A Resource Hub for Black Frontline Climate Justice Leadership</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9fcece253a314f10bf58319728cc0117-director-of-finance-the-chisholm-legacy-project-a-resource-hub-for-black-frontline-climate-justice-leadership-burtonsville</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Capital Development Services</t>
+  </si>
+  <si>
+    <t>Winston-Salem, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 84000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Health Medicine, Travel Hospitality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/5b2e58db1f1e47d2adbc87895afc1594-director-of-operations-capital-development-services-winston-salem</t>
+  </si>
+  <si>
+    <t>Director of Organizing</t>
+  </si>
+  <si>
+    <t>Fort Myers, Florida</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/488f82815a984207a363b528d3491831-director-of-organizing-direct-action-research-training-center-fort-myers</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e7171ebba5a49ae855fc2386df023dd-director-of-organizing-direct-action-research-training-center-richmond</t>
+  </si>
+  <si>
+    <t>Roanoke, Virginia</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/137cf91a1975470498e7979c9dbe056e-director-of-organizing-direct-action-research-training-center-roanoke</t>
+  </si>
+  <si>
+    <t>Director of Quality Improvement</t>
+  </si>
+  <si>
+    <t>Coalition of Orange County Community Health Centers</t>
+  </si>
+  <si>
+    <t>Orange, California</t>
+  </si>
+  <si>
+    <t>USD 99000.00 - 129000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4ada242668c4a03b12670816a2485cb-director-of-quality-improvement-coalition-of-orange-county-community-health-centers-orange</t>
+  </si>
+  <si>
+    <t>Director of Risk &amp; Safety Management</t>
+  </si>
+  <si>
+    <t>Acquire Talent Partners</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/007dd48094b448f8a22d28afc1b69b7a-director-of-risk-safety-management-acquire-talent-partners-new-york</t>
+  </si>
+  <si>
+    <t>Director of Strategy and Action</t>
+  </si>
+  <si>
+    <t>Narrative Initiative</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/747f390c702149fbadbf9172046bb10a-director-of-strategy-and-action-narrative-initiative-washington</t>
+  </si>
+  <si>
     <t>Director of Support and Education</t>
   </si>
   <si>
@@ -931,12 +1297,21 @@
     <t>USD 240.00 - 240.00/day</t>
   </si>
   <si>
-    <t>Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/8ae07f13fdb94812bbf00be1067ccf9d-english-professor-seeds-access-changes-everything-south-orange-village</t>
   </si>
   <si>
+    <t>Event Planner</t>
+  </si>
+  <si>
+    <t>The Math Learning Center</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f15da9a2147741d4b6c057dae7990028-event-planner-the-math-learning-center-portland</t>
+  </si>
+  <si>
     <t>Events &amp; Marketing Manager</t>
   </si>
   <si>
@@ -973,6 +1348,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/a785e91f11fe4537a152a523153696c0-events-and-ministry-coordinator-multiple-locations-flexible-opportunities-apartment-life-dallas</t>
   </si>
   <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>MACLA/Movimiento de Arte y Cultura Latino Americana</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>USD 31.25 - 36.06/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f388bb45b56c48528a2bd3d00ff907dc-executive-assistant-maclamovimiento-de-arte-y-cultura-latino-americana-san-jose</t>
+  </si>
+  <si>
     <t>Bellingham, Washington</t>
   </si>
   <si>
@@ -988,6 +1381,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b80c1b5e1c864f45bc7f924fc2a2224f-executive-director-wild-whatcom-bellingham</t>
   </si>
   <si>
+    <t>Executive Director - McMinnville Downtown Association</t>
+  </si>
+  <si>
+    <t>McMinnville Downtown Association</t>
+  </si>
+  <si>
+    <t>McMinnville, Oregon</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/006aba1b403147fab5700acac147c226-executive-director-mcminnville-downtown-association-mcminnville-downtown-association-mcminnville</t>
+  </si>
+  <si>
     <t>Executive Director (US-Based)</t>
   </si>
   <si>
@@ -1018,9 +1429,6 @@
     <t>Art Students League of New York</t>
   </si>
   <si>
-    <t>New York, NY</t>
-  </si>
-  <si>
     <t>USD 120000.00 - 125000.00/year</t>
   </si>
   <si>
@@ -1066,6 +1474,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/eeb42d44cce445d4bddff924336d4d60-farmers-market-manager-urban-village-farmers-market-association-san-carlos</t>
   </si>
   <si>
+    <t>Field Coordinator - SEIU Healthcare Michigan (HCMI)</t>
+  </si>
+  <si>
+    <t>SEIU</t>
+  </si>
+  <si>
+    <t>Remote (Michigan)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/b532439c89b44f4dae5816b5087769d5-field-coordinator-seiu-healthcare-michigan-hcmi-seiu-detroit</t>
+  </si>
+  <si>
     <t>Finance Associate (part-time)</t>
   </si>
   <si>
@@ -1081,6 +1504,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c0c1e9faef75473cb4754d8d12041338-finance-associate-part-time-artsconnection-new-york</t>
   </si>
   <si>
+    <t>Freelance part-time bookkeeper for small nonprofit</t>
+  </si>
+  <si>
+    <t>Earth Day Initiative</t>
+  </si>
+  <si>
+    <t>Remote (New York, New York)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Education, Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99ae67ba329b4c82a6f24cdbc16e6aed-freelance-part-time-bookkeeper-for-small-nonprofit-earth-day-initiative-new-york</t>
+  </si>
+  <si>
     <t>Geopolitics Researcher [Remote - Part Time]</t>
   </si>
   <si>
@@ -1114,6 +1555,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/7cc5347d3f95491b9b63383cc7439b3b-gift-planning-advisor-seattle-foundation-seattle</t>
   </si>
   <si>
+    <t>Grant and Contracts Manager</t>
+  </si>
+  <si>
+    <t>North East Community Center (Dutchess County, NY)</t>
+  </si>
+  <si>
+    <t>Millerton, New York</t>
+  </si>
+  <si>
+    <t>USD 32.14 - 34.62/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7af007bf7a7443a5b008188e48904f04-grant-and-contracts-manager-north-east-community-center-dutchess-county-ny-millerton</t>
+  </si>
+  <si>
     <t>National Association of Conservation Districts</t>
   </si>
   <si>
@@ -1123,6 +1582,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/e09be5f615b743b79dd25ca9126815c0-grants-administrator-national-association-of-conservation-districts-washington</t>
   </si>
   <si>
+    <t>Grants Coordinator</t>
+  </si>
+  <si>
+    <t>City of Antioch</t>
+  </si>
+  <si>
+    <t>Antioch, California</t>
+  </si>
+  <si>
+    <t>USD 95184.00 - 115692.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/cf518e462e1e48f19aeab15cf7923f44-grants-coordinator-city-of-antioch-antioch</t>
+  </si>
+  <si>
     <t>Grants Manager &amp; Partnerships Coordinator</t>
   </si>
   <si>
@@ -1150,15 +1627,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/e9829534ec794cf6b4ba0126dc45018f-graphic-designer-kaufman-music-center-new-york</t>
   </si>
   <si>
+    <t>Growth Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d7c89e3e46f544cf86f10e92a1789f9c-growth-manager-onja-toamasina</t>
+  </si>
+  <si>
     <t>International Director</t>
   </si>
   <si>
     <t>Swift Sports Organisation</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 100.00/month</t>
   </si>
   <si>
@@ -1183,6 +1663,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/f5209ab39d084e528e078ee43421072e-junior-art-director-americares-stamford</t>
   </si>
   <si>
+    <t>King County Youth Homelessness Attorney</t>
+  </si>
+  <si>
+    <t>Legal Counsel for Youth and Children</t>
+  </si>
+  <si>
+    <t>USD 82400.00 - 113300.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb995b702d0f476b92396d89a549195a-king-county-youth-homelessness-attorney-legal-counsel-for-youth-and-children-seattle</t>
+  </si>
+  <si>
     <t>Lead Canvasser</t>
   </si>
   <si>
@@ -1192,6 +1687,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/44fa7be526a74407915463e997c463d6-lead-canvasser-new-economic-justice-organizing-project-new-orleans</t>
   </si>
   <si>
+    <t>Lead Organizer - SEIU Healthcare Michigan (HCMI)</t>
+  </si>
+  <si>
+    <t>Service Employees International Union - SEIU</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/726da27919f8421f8f52ac72ac7c5f97-lead-organizer-seiu-healthcare-michigan-hcmi-service-employees-international-union-seiu-detroit</t>
+  </si>
+  <si>
+    <t>Legal Administrative Assistant II</t>
+  </si>
+  <si>
+    <t>Southern Environmental Law Center</t>
+  </si>
+  <si>
+    <t>Asheville, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 69300.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/93b868ef58f849efad20f8362265eae0-legal-administrative-assistant-ii-southern-environmental-law-center-asheville</t>
+  </si>
+  <si>
     <t>Literacy Tutor (PT, Temporary)</t>
   </si>
   <si>
@@ -1219,9 +1747,6 @@
     <t>Rome, 62, IT</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>EUR 3690.00 - 4245.00/month</t>
   </si>
   <si>
@@ -1246,6 +1771,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/f82714edb74a41c6a705e3a9d265bdcb-manager-digital-platforms-new-york-city-ballet-new-york</t>
   </si>
   <si>
+    <t>Managing Immigration Attorney</t>
+  </si>
+  <si>
+    <t>Catholic Charities of Yolo-Solano, Inc.</t>
+  </si>
+  <si>
+    <t>Fairfield, California</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12c1c79b20da4928a5d2b0cfdf167cb2-managing-immigration-attorney-catholic-charities-of-yolo-solano-inc-fairfield</t>
+  </si>
+  <si>
+    <t>Marketing and Communications Specialist</t>
+  </si>
+  <si>
+    <t>Save The Bay</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 38.34 - 38.34/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fbb6fe68e70e4ed7a82e75924c665285-marketing-and-communications-specialist-save-the-bay-oakland</t>
+  </si>
+  <si>
+    <t>National Grange - Executive Operations Assistant (Part-Time)</t>
+  </si>
+  <si>
+    <t>NeighborWorks Affiliates</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Rural Areas, Agriculture, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7865bd95780848fd99c248dc43def14a-national-grange-executive-operations-assistant-part-time-neighborworks-affiliates-washington</t>
+  </si>
+  <si>
     <t>Oceans Campaigner</t>
   </si>
   <si>
@@ -1255,12 +1828,12 @@
     <t>USD 55000.00 - 75000.00/year</t>
   </si>
   <si>
-    <t>Animals, Climate Change, Energy</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/20700ba39ad6410a888556d2d39b6974-oceans-campaigner-center-for-biological-diversity-oakland</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20700ba39ad6410a888556d2d39b6974-oceans-campaigner-center-for-biological-diversity-new-orleans</t>
+  </si>
+  <si>
     <t>Operations and Finance Manager</t>
   </si>
   <si>
@@ -1288,6 +1861,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/14b14f2837904958b1bd7bd9451c5e9a-operations-coordinator-30hrweek-hybridprinceton-nj-young-audiences-new-jersey-eastern-pennsylvania-princeton</t>
   </si>
   <si>
+    <t>Operations Officer</t>
+  </si>
+  <si>
+    <t>Legal Advocates for Safe Science and Technology</t>
+  </si>
+  <si>
+    <t>Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2c0f9a8e0fc47dc9679f16d26bff0be-operations-officer-legal-advocates-for-safe-science-and-technology-new-york</t>
+  </si>
+  <si>
     <t>Organizer</t>
   </si>
   <si>
@@ -1303,6 +1888,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/18440839e1754303a411879d4ea95052-organizer-youth-represent-new-york</t>
   </si>
   <si>
+    <t>Outward Bound Customer Success Specialist</t>
+  </si>
+  <si>
+    <t>Outward Bound USA</t>
+  </si>
+  <si>
+    <t>USD 19.23 - 22.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/158bcc90511149be9049b903e0325491-outward-bound-customer-success-specialist-outward-bound-usa-boulder</t>
+  </si>
+  <si>
     <t>Paralegal</t>
   </si>
   <si>
@@ -1342,6 +1942,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/dc49385d870d48b99c26e593c7592877-part-time-management-accountant-accelerating-circularity-inc-middletown</t>
   </si>
   <si>
+    <t>Part-time Math Instructional Coach serving Newcomer Multilingual Learners</t>
+  </si>
+  <si>
+    <t>Bridges to Academic Success</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 50.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f3e093fea2243abb3be6d3097198267-part-time-math-instructional-coach-serving-newcomer-multilingual-learners-bridges-to-academic-success-new-york</t>
+  </si>
+  <si>
     <t>People &amp; Culture Director</t>
   </si>
   <si>
@@ -1387,6 +2002,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/92f2d8d6a241490f9002c479df933dae-play-for-pink-associate-fundraising-operations-the-breast-cancer-research-foundation-new-york</t>
   </si>
   <si>
+    <t>Policy Organizer</t>
+  </si>
+  <si>
+    <t>Youth Empowerment for Advancement Hangout (YEAH Inc.)</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Policy, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c488aa8539d54d3485d65972eb5281a9-policy-organizer-youth-empowerment-for-advancement-hangout-yeah-inc-philadelphia</t>
+  </si>
+  <si>
     <t>Polycapital Academy Lead</t>
   </si>
   <si>
@@ -1414,6 +2044,21 @@
     <t>https://www.idealist.org/en/government-job/2ccdec4c9b8440a48276f7770ad6c147-post-baccalaureatepost-doctoral-bioethics-fellowship-at-the-nih-department-of-bioethics-clinical-center-national-institutes-of-health-bethesda</t>
   </si>
   <si>
+    <t>President</t>
+  </si>
+  <si>
+    <t>The Seattle School of Theology &amp; Psychology</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f9fbf7e091f94a9e82a4377b43a82a80-president-the-seattle-school-of-theology-psychology-seattle</t>
+  </si>
+  <si>
     <t>Press Secretary and Media Relations Manager</t>
   </si>
   <si>
@@ -1519,6 +2164,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/48224d9e06d14a788aaa78ef87eb67d0-program-manager-jcc-maccabi-jcc-association-kings-county</t>
   </si>
   <si>
+    <t>Program Officer, Climate</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21850c973c594757a6598c2b4023904c-program-officer-climate-barr-foundation-boston</t>
+  </si>
+  <si>
     <t>Public Benefits Staff Attorney</t>
   </si>
   <si>
@@ -1555,6 +2212,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/01b927f40d1a451586f996ecff257858-resident-services-coordinator-native-american-youth-and-family-center-naya-portland</t>
   </si>
   <si>
+    <t>SACRED Organizing Fellowship (Paid, Part-time, Contract)</t>
+  </si>
+  <si>
+    <t>SACRED</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/259fc8d4596e44f5b7ad38f4d700d3d6-sacred-organizing-fellowship-paid-part-time-contract-sacred-chicago</t>
+  </si>
+  <si>
+    <t>Salesforce &amp; Systems Administrator</t>
+  </si>
+  <si>
+    <t>Spark the Journey</t>
+  </si>
+  <si>
+    <t>USD 69000.00 - 79000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3af66bc5af74cf781cc6f0c39fb4428-salesforce-systems-administrator-spark-the-journey-washington</t>
+  </si>
+  <si>
+    <t>Senior Communications Officer</t>
+  </si>
+  <si>
+    <t>Equimundo</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb91e80bdeda401cabdc01a4f0be534e-senior-communications-officer-equimundo-washington</t>
+  </si>
+  <si>
     <t>Senior Counsel/Advisor</t>
   </si>
   <si>
@@ -1567,6 +2266,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/851e16c84993414981bc54c1cdb8c30e-senior-counseladvisor-afl-cio-tech-institute-washington</t>
   </si>
   <si>
+    <t>Senior Director of Development</t>
+  </si>
+  <si>
+    <t>Huckleberry Youth Programs</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50a29e09a5614a02b1ce2d479a24c1ac-senior-director-of-development-huckleberry-youth-programs-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Director of HR and Operations</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5a148833d3e4d639eac908dfc41bb35-senior-director-of-hr-and-operations-huckleberry-youth-programs-san-francisco</t>
+  </si>
+  <si>
     <t>Senior Director, Foundation Relations</t>
   </si>
   <si>
@@ -1582,6 +2311,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/3b8760473c9d4cfbbe7d4661f2b3f53f-senior-director-foundation-relations-alliance-for-justice-washington</t>
   </si>
   <si>
+    <t>Senior Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>CAREGIVERS:Volunteers Assisting the Elderly</t>
+  </si>
+  <si>
+    <t>Ventura, California</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Seniors Retirement, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/621156ab1f8646ddaff90361e3a0170d-senior-engagement-coordinator-caregiversvolunteers-assisting-the-elderly-ventura</t>
+  </si>
+  <si>
+    <t>Senior Events Associate</t>
+  </si>
+  <si>
+    <t>The Honorable Tina Brozman Foundation for Ovarian Cancer Research (Tina's Wish)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd517c57f9e34922950d24108afcf517-senior-events-associate-the-honorable-tina-brozman-foundation-for-ovarian-cancer-research-tinas-wish-new-york</t>
+  </si>
+  <si>
+    <t>Senior Finance Coordinator, AEL II (Hybrid) - (3870)</t>
+  </si>
+  <si>
+    <t>Institute of International Education</t>
+  </si>
+  <si>
+    <t>USD 54056.12 - 54056.12/year</t>
+  </si>
+  <si>
+    <t>Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7f7f2b1b4fe4eca85291edf9776e92b-senior-finance-coordinator-ael-ii-hybrid-3870-institute-of-international-education-new-york</t>
+  </si>
+  <si>
     <t>Senior Foundation Relations Manager</t>
   </si>
   <si>
@@ -1591,18 +2368,72 @@
     <t>https://www.idealist.org/en/nonprofit-job/bc360ac9e0a24d45a4fab94566e07f3d-senior-foundation-relations-manager-alliance-for-justice-washington</t>
   </si>
   <si>
+    <t>Senior Managing Director of Advancement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/07023117d739460b9deccc6d42cb5f6b-senior-managing-director-of-advancement-the-chisholm-legacy-project-a-resource-hub-for-black-frontline-climate-justice-leadership-burtonsville</t>
+  </si>
+  <si>
     <t>Senior Managing Director of Organizing</t>
   </si>
   <si>
-    <t>The Chisholm Legacy Project: A Resource Hub for Black Frontline Climate Justice Leadership</t>
-  </si>
-  <si>
-    <t>Climate Change, Community Development, Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/a8ab38ef87a54be8b237024768e48768-senior-managing-director-of-organizing-the-chisholm-legacy-project-a-resource-hub-for-black-frontline-climate-justice-leadership-burtonsville</t>
   </si>
   <si>
+    <t>Senior Program Manager, Government Partnerships</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8407f27ce8d3410fad1202cf9d9e5853-senior-program-manager-government-partnerships-baby2baby-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Public Speaking Coach</t>
+  </si>
+  <si>
+    <t>PRACTICE SPACE INC</t>
+  </si>
+  <si>
+    <t>Richmond, California</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cac5c38d958c4baca322582ae35d63cc-senior-public-speaking-coach-practice-space-inc-richmond</t>
+  </si>
+  <si>
+    <t>Site Director (Berkekley)</t>
+  </si>
+  <si>
+    <t>The Multicultural Institute, Berkeley</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 71000.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Immigrants Or Refugees, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/becf5fdf701f43b487696a89c0ad0368-site-director-berkekley-the-multicultural-institute-berkeley-berkeley</t>
+  </si>
+  <si>
     <t>Social Media and Community Manager</t>
   </si>
   <si>
@@ -1660,6 +2491,12 @@
     <t>https://www.idealist.org/en/government-job/b2d99d7a43264212b3254fe6fc12c0aa-social-worker-town-of-ashland-department-of-prevention-human-services-ashland</t>
   </si>
   <si>
+    <t>Special Projects Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2490a1a060074997abd08d532a8d77a2-special-projects-manager-onja-toamasina</t>
+  </si>
+  <si>
     <t>Staff Assistant</t>
   </si>
   <si>
@@ -1678,6 +2515,24 @@
     <t>https://www.idealist.org/en/government-job/a39760369e944cadacdaf312dbb6b6ad-staff-assistant-office-of-senator-peter-welch-burlington</t>
   </si>
   <si>
+    <t>Staff Attorney / Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of Minnesota</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b4d8d8603b04a48ae4d5be005da0d62-staff-attorney-senior-staff-attorney-american-civil-liberties-union-of-minnesota-minneapolis</t>
+  </si>
+  <si>
     <t>Supervising Attorney</t>
   </si>
   <si>
@@ -1690,21 +2545,99 @@
     <t>https://www.idealist.org/en/nonprofit-job/b7474f682b41421abb6f82c8353c74f2-supervising-attorney-unlocal-inc-new-york</t>
   </si>
   <si>
+    <t>Supervising Attorney Housing (Hybrid)</t>
+  </si>
+  <si>
+    <t>Norwalk, California</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dadc3427f9cf4396b0c61af37d0e83a2-supervising-attorney-housing-hybrid-community-legal-aid-so-cal-norwalk</t>
+  </si>
+  <si>
+    <t>Supervising Attorney, NYC</t>
+  </si>
+  <si>
+    <t>Safe Passage Project Corporation</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d19363b7f8a7442b9b1bfb9fd191dec4-supervising-attorney-nyc-safe-passage-project-corporation-new-york</t>
+  </si>
+  <si>
     <t>Technical Support Specialist</t>
   </si>
   <si>
     <t>Civilization Research Institute</t>
   </si>
   <si>
-    <t>Asheville, North Carolina</t>
-  </si>
-  <si>
     <t>Environment, Policy, Research Social Science</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/e9564fc725d842969eb49aef7964f913-technical-support-specialist-civilization-research-institute-asheville</t>
   </si>
   <si>
+    <t>Therapist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f8218e4c82c4763b9d403a931cf665f-therapist-onja-toamasina</t>
+  </si>
+  <si>
+    <t>TN Healthy Schools Specialist (TN ONLY)</t>
+  </si>
+  <si>
+    <t>Action for Healthy Kids</t>
+  </si>
+  <si>
+    <t>Remote (Tennessee)</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba183eb3a6094a7091eb0059e93ede67-tn-healthy-schools-specialist-tn-only-action-for-healthy-kids-chicago</t>
+  </si>
+  <si>
+    <t>US Graphic Designer</t>
+  </si>
+  <si>
+    <t>Elba Hope Foundation</t>
+  </si>
+  <si>
+    <t>USD 150.00 - 750.00/month</t>
+  </si>
+  <si>
+    <t>Agriculture, Children Youth, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f372ea2e54474d25902ca762010372fb-us-graphic-designer-elba-hope-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Veterinarian Needed for Los Angeles-based Cat Rescue</t>
+  </si>
+  <si>
+    <t>Stray Cat Alliance</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Community Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/969b3243c7974db08fca7c1e1f84ba68-veterinarian-needed-for-los-angeles-based-cat-rescue-stray-cat-alliance-los-angeles</t>
+  </si>
+  <si>
     <t>Vice President, Advancement and Philanthropic Engagement, Institute for Women's Policy Research</t>
   </si>
   <si>
@@ -1715,6 +2648,60 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/job/f5d68abac8bf4a5992fa10d2bfe0071a-vice-president-advancement-and-philanthropic-engagement-institute-for-womens-policy-research-institute-for-womens-policy-research-washington</t>
+  </si>
+  <si>
+    <t>Violent Crime Initiative Advocate</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b358c0d517c942648f5782f211089098-violent-crime-initiative-advocate-youth-empowerment-for-advancement-hangout-yeah-inc-philadelphia</t>
+  </si>
+  <si>
+    <t>Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>ServeWyoming</t>
+  </si>
+  <si>
+    <t>Casper, Wyoming</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Crime Safety, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c47fabca1f5646fa96b386207a31168d-volunteer-coordinator-servewyoming-casper</t>
+  </si>
+  <si>
+    <t>VP Chief Marketing Officer</t>
+  </si>
+  <si>
+    <t>The Frank Lloyd Wright Foundation</t>
+  </si>
+  <si>
+    <t>Scottsdale, Arizona</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/287883119c9d42b0a68a66eb9b0b5019-vp-chief-marketing-officer-the-frank-lloyd-wright-foundation-scottsdale</t>
+  </si>
+  <si>
+    <t>Work Readiness Coordinator - Career Pathway Connections</t>
+  </si>
+  <si>
+    <t>LA Promise Fund</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 72400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea55014ff89141d880c46c296c8ec89d-work-readiness-coordinator-career-pathway-connections-la-promise-fund-los-angeles</t>
   </si>
 </sst>
 </file>
@@ -2849,7 +3836,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2888,8 +3875,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2897,7 +3910,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2938,384 +3951,384 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F3" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E4" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D7" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E7" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="F8" t="s">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B9" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D9" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E9" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="F9" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C10" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D10" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E10" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="D11" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="E11" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F11" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B12" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="D12" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E12" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E13" t="s">
+        <v>229</v>
+      </c>
+      <c r="F13" t="s">
         <v>176</v>
       </c>
-      <c r="D13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E13" t="s">
-        <v>221</v>
-      </c>
-      <c r="F13" t="s">
-        <v>218</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B14" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C14" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D14" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="E14" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F14" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C15" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D15" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F15" t="s">
-        <v>234</v>
+        <v>176</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B16" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C16" t="s">
         <v>238</v>
       </c>
       <c r="D16" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E16" t="s">
+        <v>234</v>
+      </c>
+      <c r="F16" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F16" t="s">
-        <v>240</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" t="s">
+        <v>241</v>
+      </c>
+      <c r="C17" t="s">
         <v>242</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
+        <v>183</v>
+      </c>
+      <c r="E17" t="s">
         <v>243</v>
       </c>
-      <c r="C17" t="s">
+      <c r="F17" t="s">
         <v>244</v>
       </c>
-      <c r="D17" t="s">
-        <v>177</v>
-      </c>
-      <c r="E17" t="s">
-        <v>217</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="H17" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>246</v>
+      </c>
+      <c r="B18" t="s">
         <v>247</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>248</v>
       </c>
-      <c r="C18" t="s">
-        <v>176</v>
-      </c>
       <c r="D18" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E18" t="s">
         <v>249</v>
@@ -3335,39 +4348,39 @@
         <v>253</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="D19" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E20" t="s">
-        <v>169</v>
+        <v>259</v>
       </c>
       <c r="F20" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>260</v>
@@ -3381,194 +4394,194 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
+        <v>210</v>
+      </c>
+      <c r="D21" t="s">
+        <v>183</v>
+      </c>
+      <c r="E21" t="s">
+        <v>249</v>
+      </c>
+      <c r="F21" t="s">
+        <v>176</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="D21" t="s">
-        <v>177</v>
-      </c>
-      <c r="E21" t="s">
-        <v>264</v>
-      </c>
-      <c r="F21" t="s">
-        <v>194</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" t="s">
+        <v>265</v>
+      </c>
+      <c r="C22" t="s">
+        <v>210</v>
+      </c>
+      <c r="D22" t="s">
         <v>266</v>
       </c>
-      <c r="B22" t="s">
+      <c r="E22" t="s">
         <v>267</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F22" t="s">
         <v>268</v>
       </c>
-      <c r="D22" t="s">
-        <v>167</v>
-      </c>
-      <c r="E22" t="s">
-        <v>169</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="H22" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>270</v>
+      </c>
+      <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" t="s">
         <v>272</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" t="s">
         <v>273</v>
       </c>
-      <c r="D23" t="s">
-        <v>177</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="H23" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="F23" t="s">
-        <v>169</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" t="s">
+        <v>271</v>
+      </c>
+      <c r="C24" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" t="s">
         <v>276</v>
       </c>
-      <c r="B24" t="s">
+      <c r="F24" t="s">
+        <v>273</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="C24" t="s">
-        <v>176</v>
-      </c>
-      <c r="D24" t="s">
-        <v>177</v>
-      </c>
-      <c r="E24" t="s">
-        <v>278</v>
-      </c>
-      <c r="F24" t="s">
-        <v>279</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>278</v>
+      </c>
+      <c r="B25" t="s">
+        <v>279</v>
+      </c>
+      <c r="C25" t="s">
+        <v>280</v>
+      </c>
+      <c r="D25" t="s">
         <v>281</v>
       </c>
-      <c r="B25" t="s">
+      <c r="E25" t="s">
         <v>282</v>
       </c>
-      <c r="C25" t="s">
-        <v>273</v>
-      </c>
-      <c r="D25" t="s">
-        <v>177</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>283</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>285</v>
+      </c>
+      <c r="B26" t="s">
         <v>286</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>287</v>
       </c>
-      <c r="C26" t="s">
-        <v>176</v>
-      </c>
       <c r="D26" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E26" t="s">
-        <v>169</v>
+        <v>288</v>
       </c>
       <c r="F26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D27" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E27" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F27" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B28" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>299</v>
       </c>
       <c r="D28" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E28" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="F28" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C29" t="s">
-        <v>303</v>
+        <v>166</v>
       </c>
       <c r="D29" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="E29" t="s">
         <v>304</v>
@@ -3588,1218 +4601,2874 @@
         <v>308</v>
       </c>
       <c r="C30" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" t="s">
         <v>309</v>
       </c>
-      <c r="D30" t="s">
-        <v>177</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>310</v>
       </c>
-      <c r="F30" t="s">
+      <c r="H30" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>312</v>
+      </c>
+      <c r="B31" t="s">
         <v>313</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>248</v>
+      </c>
+      <c r="D31" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" t="s">
+        <v>249</v>
+      </c>
+      <c r="F31" t="s">
+        <v>200</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="C31" t="s">
-        <v>315</v>
-      </c>
-      <c r="D31" t="s">
-        <v>177</v>
-      </c>
-      <c r="E31" t="s">
-        <v>316</v>
-      </c>
-      <c r="F31" t="s">
-        <v>317</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>316</v>
       </c>
       <c r="C32" t="s">
+        <v>317</v>
+      </c>
+      <c r="D32" t="s">
+        <v>183</v>
+      </c>
+      <c r="E32" t="s">
+        <v>318</v>
+      </c>
+      <c r="F32" t="s">
         <v>319</v>
       </c>
-      <c r="D32" t="s">
-        <v>177</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="H32" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="F32" t="s">
-        <v>321</v>
-      </c>
-      <c r="G32" t="s">
-        <v>322</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>321</v>
+      </c>
+      <c r="B33" t="s">
+        <v>322</v>
+      </c>
+      <c r="C33" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" t="s">
+        <v>183</v>
+      </c>
+      <c r="E33" t="s">
+        <v>176</v>
+      </c>
+      <c r="F33" t="s">
+        <v>323</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="B33" t="s">
-        <v>325</v>
-      </c>
-      <c r="C33" t="s">
-        <v>176</v>
-      </c>
-      <c r="D33" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33" t="s">
-        <v>203</v>
-      </c>
-      <c r="F33" t="s">
-        <v>326</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>325</v>
+      </c>
+      <c r="B34" t="s">
+        <v>326</v>
+      </c>
+      <c r="C34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D34" t="s">
+        <v>183</v>
+      </c>
+      <c r="E34" t="s">
         <v>328</v>
       </c>
-      <c r="B34" t="s">
+      <c r="F34" t="s">
+        <v>200</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="C34" t="s">
-        <v>238</v>
-      </c>
-      <c r="D34" t="s">
-        <v>177</v>
-      </c>
-      <c r="E34" t="s">
-        <v>310</v>
-      </c>
-      <c r="F34" t="s">
-        <v>330</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>330</v>
+      </c>
+      <c r="B35" t="s">
+        <v>331</v>
+      </c>
+      <c r="C35" t="s">
         <v>332</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" t="s">
+        <v>176</v>
+      </c>
+      <c r="F35" t="s">
         <v>333</v>
       </c>
-      <c r="C35" t="s">
+      <c r="H35" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="D35" t="s">
-        <v>177</v>
-      </c>
-      <c r="E35" t="s">
-        <v>335</v>
-      </c>
-      <c r="F35" t="s">
-        <v>336</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>335</v>
+      </c>
+      <c r="B36" t="s">
+        <v>336</v>
+      </c>
+      <c r="C36" t="s">
+        <v>337</v>
+      </c>
+      <c r="D36" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" t="s">
+        <v>176</v>
+      </c>
+      <c r="F36" t="s">
+        <v>176</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="B36" t="s">
-        <v>339</v>
-      </c>
-      <c r="C36" t="s">
-        <v>340</v>
-      </c>
-      <c r="D36" t="s">
-        <v>177</v>
-      </c>
-      <c r="E36" t="s">
-        <v>341</v>
-      </c>
-      <c r="F36" t="s">
-        <v>342</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C37" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="D37" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="E37" t="s">
-        <v>347</v>
+        <v>176</v>
       </c>
       <c r="F37" t="s">
-        <v>348</v>
+        <v>176</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C38" t="s">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="D38" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="E38" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="F38" t="s">
-        <v>353</v>
+        <v>176</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C39" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D39" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="E39" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="F39" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="C40" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="D40" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E40" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="F40" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C41" t="s">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="D41" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E41" t="s">
-        <v>203</v>
+        <v>357</v>
       </c>
       <c r="F41" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C42" t="s">
-        <v>371</v>
+        <v>166</v>
       </c>
       <c r="D42" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E42" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F42" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B43" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C43" t="s">
-        <v>273</v>
+        <v>366</v>
       </c>
       <c r="D43" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E43" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="F43" t="s">
-        <v>353</v>
+        <v>256</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B44" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="C44" t="s">
+        <v>366</v>
+      </c>
+      <c r="D44" t="s">
+        <v>183</v>
+      </c>
+      <c r="E44" t="s">
+        <v>370</v>
+      </c>
+      <c r="F44" t="s">
         <v>176</v>
       </c>
-      <c r="D44" t="s">
-        <v>380</v>
-      </c>
-      <c r="E44" t="s">
-        <v>381</v>
-      </c>
-      <c r="F44" t="s">
-        <v>382</v>
-      </c>
       <c r="H44" s="2" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="C45" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D45" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E45" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="F45" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B46" t="s">
-        <v>224</v>
+        <v>378</v>
       </c>
       <c r="C46" t="s">
-        <v>225</v>
+        <v>379</v>
       </c>
       <c r="D46" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="E46" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="F46" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C47" t="s">
-        <v>394</v>
+        <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="E47" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="F47" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C48" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="D48" t="s">
-        <v>401</v>
+        <v>183</v>
       </c>
       <c r="E48" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F48" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s">
-        <v>406</v>
+        <v>232</v>
       </c>
       <c r="C49" t="s">
-        <v>334</v>
+        <v>394</v>
       </c>
       <c r="D49" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E49" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="F49" t="s">
-        <v>408</v>
+        <v>176</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s">
-        <v>411</v>
+        <v>232</v>
       </c>
       <c r="C50" t="s">
+        <v>397</v>
+      </c>
+      <c r="D50" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50" t="s">
+        <v>398</v>
+      </c>
+      <c r="F50" t="s">
         <v>176</v>
       </c>
-      <c r="D50" t="s">
-        <v>177</v>
-      </c>
-      <c r="E50" t="s">
-        <v>412</v>
-      </c>
-      <c r="F50" t="s">
-        <v>413</v>
-      </c>
       <c r="H50" s="2" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s">
-        <v>416</v>
+        <v>232</v>
       </c>
       <c r="C51" t="s">
+        <v>400</v>
+      </c>
+      <c r="D51" t="s">
+        <v>183</v>
+      </c>
+      <c r="E51" t="s">
+        <v>401</v>
+      </c>
+      <c r="F51" t="s">
         <v>176</v>
       </c>
-      <c r="D51" t="s">
-        <v>177</v>
-      </c>
-      <c r="E51" t="s">
-        <v>264</v>
-      </c>
-      <c r="F51" t="s">
-        <v>417</v>
-      </c>
       <c r="H51" s="2" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="B52" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="C52" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="D52" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E52" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="F52" t="s">
-        <v>353</v>
+        <v>176</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="C53" t="s">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="D53" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E53" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="F53" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C54" t="s">
-        <v>273</v>
+        <v>166</v>
       </c>
       <c r="D54" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E54" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="F54" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="C55" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D55" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="E55" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="F55" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="C56" t="s">
-        <v>176</v>
+        <v>425</v>
       </c>
       <c r="D56" t="s">
-        <v>167</v>
+        <v>281</v>
       </c>
       <c r="E56" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="F56" t="s">
-        <v>440</v>
+        <v>268</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="C57" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="D57" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E57" t="s">
-        <v>445</v>
+        <v>176</v>
       </c>
       <c r="F57" t="s">
-        <v>336</v>
+        <v>176</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C58" t="s">
-        <v>176</v>
+        <v>434</v>
       </c>
       <c r="D58" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E58" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="F58" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="B59" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="C59" t="s">
-        <v>273</v>
+        <v>440</v>
       </c>
       <c r="D59" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E59" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F59" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="B60" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="C60" t="s">
-        <v>176</v>
+        <v>446</v>
       </c>
       <c r="D60" t="s">
-        <v>380</v>
+        <v>183</v>
       </c>
       <c r="E60" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="F60" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>462</v>
+        <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>463</v>
+        <v>74</v>
       </c>
       <c r="C61" t="s">
-        <v>232</v>
+        <v>450</v>
       </c>
       <c r="D61" t="s">
-        <v>401</v>
+        <v>183</v>
       </c>
       <c r="E61" t="s">
-        <v>169</v>
+        <v>451</v>
       </c>
       <c r="F61" t="s">
-        <v>464</v>
+        <v>452</v>
+      </c>
+      <c r="G61" t="s">
+        <v>453</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="B62" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="C62" t="s">
-        <v>238</v>
+        <v>457</v>
       </c>
       <c r="D62" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E62" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="F62" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B63" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C63" t="s">
-        <v>273</v>
+        <v>166</v>
       </c>
       <c r="D63" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E63" t="s">
-        <v>473</v>
+        <v>221</v>
       </c>
       <c r="F63" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="B64" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="C64" t="s">
-        <v>478</v>
+        <v>293</v>
       </c>
       <c r="D64" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E64" t="s">
-        <v>479</v>
+        <v>435</v>
       </c>
       <c r="F64" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="B65" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="C65" t="s">
-        <v>484</v>
+        <v>248</v>
       </c>
       <c r="D65" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E65" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="F65" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="B66" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="C66" t="s">
-        <v>198</v>
+        <v>476</v>
       </c>
       <c r="D66" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E66" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="F66" t="s">
-        <v>234</v>
+        <v>478</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B67" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C67" t="s">
-        <v>273</v>
+        <v>482</v>
       </c>
       <c r="D67" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E67" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="F67" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="B68" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C68" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D68" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E68" t="s">
-        <v>203</v>
+        <v>489</v>
       </c>
       <c r="F68" t="s">
-        <v>499</v>
+        <v>176</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="B69" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C69" t="s">
-        <v>503</v>
+        <v>214</v>
       </c>
       <c r="D69" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E69" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="F69" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="B70" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="C70" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="D70" t="s">
-        <v>177</v>
+        <v>499</v>
       </c>
       <c r="E70" t="s">
-        <v>510</v>
+        <v>176</v>
       </c>
       <c r="F70" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="B71" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="C71" t="s">
-        <v>238</v>
+        <v>166</v>
       </c>
       <c r="D71" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="F71" t="s">
-        <v>228</v>
+        <v>505</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="B72" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C72" t="s">
-        <v>176</v>
+        <v>509</v>
       </c>
       <c r="D72" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E72" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="F72" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s">
+        <v>514</v>
+      </c>
+      <c r="C73" t="s">
+        <v>515</v>
+      </c>
+      <c r="D73" t="s">
+        <v>183</v>
+      </c>
+      <c r="E73" t="s">
+        <v>516</v>
+      </c>
+      <c r="F73" t="s">
+        <v>517</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="C73" t="s">
-        <v>176</v>
-      </c>
-      <c r="D73" t="s">
-        <v>177</v>
-      </c>
-      <c r="E73" t="s">
-        <v>523</v>
-      </c>
-      <c r="F73" t="s">
-        <v>520</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>525</v>
+        <v>95</v>
       </c>
       <c r="B74" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="C74" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D74" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E74" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="F74" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B75" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="C75" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="D75" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E75" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="F75" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B76" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="C76" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="D76" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E76" t="s">
-        <v>538</v>
+        <v>176</v>
       </c>
       <c r="F76" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>533</v>
+      </c>
+      <c r="B77" t="s">
+        <v>534</v>
+      </c>
+      <c r="C77" t="s">
+        <v>214</v>
+      </c>
+      <c r="D77" t="s">
+        <v>183</v>
+      </c>
+      <c r="E77" t="s">
         <v>535</v>
       </c>
-      <c r="B77" t="s">
+      <c r="F77" t="s">
+        <v>494</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="C77" t="s">
-        <v>541</v>
-      </c>
-      <c r="D77" t="s">
-        <v>177</v>
-      </c>
-      <c r="E77" t="s">
-        <v>538</v>
-      </c>
-      <c r="F77" t="s">
-        <v>539</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B78" t="s">
-        <v>544</v>
+        <v>336</v>
       </c>
       <c r="C78" t="s">
-        <v>545</v>
+        <v>337</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E78" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="F78" t="s">
-        <v>546</v>
+        <v>176</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="B79" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="C79" t="s">
-        <v>550</v>
+        <v>166</v>
       </c>
       <c r="D79" t="s">
-        <v>177</v>
+        <v>499</v>
       </c>
       <c r="E79" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="F79" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="B80" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="C80" t="s">
-        <v>273</v>
+        <v>166</v>
       </c>
       <c r="D80" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E80" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="F80" t="s">
-        <v>218</v>
+        <v>547</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="B81" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="C81" t="s">
-        <v>560</v>
+        <v>509</v>
       </c>
       <c r="D81" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E81" t="s">
-        <v>169</v>
+        <v>551</v>
       </c>
       <c r="F81" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>554</v>
+      </c>
+      <c r="B82" t="s">
+        <v>279</v>
+      </c>
+      <c r="C82" t="s">
+        <v>280</v>
+      </c>
+      <c r="D82" t="s">
+        <v>281</v>
+      </c>
+      <c r="E82" t="s">
+        <v>555</v>
+      </c>
+      <c r="F82" t="s">
+        <v>283</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>557</v>
+      </c>
+      <c r="B83" t="s">
+        <v>558</v>
+      </c>
+      <c r="C83" t="s">
+        <v>559</v>
+      </c>
+      <c r="D83" t="s">
+        <v>183</v>
+      </c>
+      <c r="E83" t="s">
+        <v>560</v>
+      </c>
+      <c r="F83" t="s">
+        <v>176</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>562</v>
+      </c>
+      <c r="B84" t="s">
         <v>563</v>
       </c>
-      <c r="B82" t="s">
-        <v>237</v>
-      </c>
-      <c r="C82" t="s">
-        <v>238</v>
-      </c>
-      <c r="D82" t="s">
-        <v>177</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="C84" t="s">
         <v>564</v>
       </c>
-      <c r="F82" t="s">
+      <c r="D84" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" t="s">
         <v>565</v>
       </c>
-      <c r="H82" s="2" t="s">
+      <c r="F84" t="s">
         <v>566</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>568</v>
+      </c>
+      <c r="B85" t="s">
+        <v>569</v>
+      </c>
+      <c r="C85" t="s">
+        <v>570</v>
+      </c>
+      <c r="D85" t="s">
+        <v>281</v>
+      </c>
+      <c r="E85" t="s">
+        <v>571</v>
+      </c>
+      <c r="F85" t="s">
+        <v>572</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>574</v>
+      </c>
+      <c r="B86" t="s">
+        <v>575</v>
+      </c>
+      <c r="C86" t="s">
+        <v>576</v>
+      </c>
+      <c r="D86" t="s">
+        <v>266</v>
+      </c>
+      <c r="E86" t="s">
+        <v>577</v>
+      </c>
+      <c r="F86" t="s">
+        <v>578</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>580</v>
+      </c>
+      <c r="B87" t="s">
+        <v>581</v>
+      </c>
+      <c r="C87" t="s">
+        <v>248</v>
+      </c>
+      <c r="D87" t="s">
+        <v>183</v>
+      </c>
+      <c r="E87" t="s">
+        <v>582</v>
+      </c>
+      <c r="F87" t="s">
+        <v>583</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>585</v>
+      </c>
+      <c r="B88" t="s">
+        <v>586</v>
+      </c>
+      <c r="C88" t="s">
+        <v>587</v>
+      </c>
+      <c r="D88" t="s">
+        <v>183</v>
+      </c>
+      <c r="E88" t="s">
+        <v>588</v>
+      </c>
+      <c r="F88" t="s">
+        <v>176</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>590</v>
+      </c>
+      <c r="B89" t="s">
+        <v>591</v>
+      </c>
+      <c r="C89" t="s">
+        <v>592</v>
+      </c>
+      <c r="D89" t="s">
+        <v>183</v>
+      </c>
+      <c r="E89" t="s">
+        <v>593</v>
+      </c>
+      <c r="F89" t="s">
+        <v>594</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>596</v>
+      </c>
+      <c r="B90" t="s">
+        <v>597</v>
+      </c>
+      <c r="C90" t="s">
+        <v>166</v>
+      </c>
+      <c r="D90" t="s">
+        <v>174</v>
+      </c>
+      <c r="E90" t="s">
+        <v>598</v>
+      </c>
+      <c r="F90" t="s">
+        <v>599</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>601</v>
+      </c>
+      <c r="B91" t="s">
+        <v>602</v>
+      </c>
+      <c r="C91" t="s">
+        <v>166</v>
+      </c>
+      <c r="D91" t="s">
+        <v>183</v>
+      </c>
+      <c r="E91" t="s">
+        <v>603</v>
+      </c>
+      <c r="F91" t="s">
+        <v>566</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>601</v>
+      </c>
+      <c r="B92" t="s">
+        <v>602</v>
+      </c>
+      <c r="C92" t="s">
+        <v>166</v>
+      </c>
+      <c r="D92" t="s">
+        <v>183</v>
+      </c>
+      <c r="E92" t="s">
+        <v>603</v>
+      </c>
+      <c r="F92" t="s">
+        <v>566</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>606</v>
+      </c>
+      <c r="B93" t="s">
+        <v>607</v>
+      </c>
+      <c r="C93" t="s">
+        <v>166</v>
+      </c>
+      <c r="D93" t="s">
+        <v>183</v>
+      </c>
+      <c r="E93" t="s">
+        <v>328</v>
+      </c>
+      <c r="F93" t="s">
+        <v>608</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>610</v>
+      </c>
+      <c r="B94" t="s">
+        <v>611</v>
+      </c>
+      <c r="C94" t="s">
+        <v>612</v>
+      </c>
+      <c r="D94" t="s">
+        <v>183</v>
+      </c>
+      <c r="E94" t="s">
+        <v>613</v>
+      </c>
+      <c r="F94" t="s">
+        <v>494</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>615</v>
+      </c>
+      <c r="B95" t="s">
+        <v>616</v>
+      </c>
+      <c r="C95" t="s">
+        <v>166</v>
+      </c>
+      <c r="D95" t="s">
+        <v>183</v>
+      </c>
+      <c r="E95" t="s">
+        <v>272</v>
+      </c>
+      <c r="F95" t="s">
+        <v>617</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>619</v>
+      </c>
+      <c r="B96" t="s">
+        <v>620</v>
+      </c>
+      <c r="C96" t="s">
+        <v>214</v>
+      </c>
+      <c r="D96" t="s">
+        <v>183</v>
+      </c>
+      <c r="E96" t="s">
+        <v>621</v>
+      </c>
+      <c r="F96" t="s">
+        <v>622</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>624</v>
+      </c>
+      <c r="B97" t="s">
+        <v>625</v>
+      </c>
+      <c r="C97" t="s">
+        <v>166</v>
+      </c>
+      <c r="D97" t="s">
+        <v>183</v>
+      </c>
+      <c r="E97" t="s">
+        <v>626</v>
+      </c>
+      <c r="F97" t="s">
+        <v>627</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>629</v>
+      </c>
+      <c r="B98" t="s">
+        <v>620</v>
+      </c>
+      <c r="C98" t="s">
+        <v>214</v>
+      </c>
+      <c r="D98" t="s">
+        <v>183</v>
+      </c>
+      <c r="E98" t="s">
+        <v>630</v>
+      </c>
+      <c r="F98" t="s">
+        <v>622</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>632</v>
+      </c>
+      <c r="B99" t="s">
+        <v>633</v>
+      </c>
+      <c r="C99" t="s">
+        <v>166</v>
+      </c>
+      <c r="D99" t="s">
+        <v>281</v>
+      </c>
+      <c r="E99" t="s">
+        <v>634</v>
+      </c>
+      <c r="F99" t="s">
+        <v>635</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>637</v>
+      </c>
+      <c r="B100" t="s">
+        <v>638</v>
+      </c>
+      <c r="C100" t="s">
+        <v>166</v>
+      </c>
+      <c r="D100" t="s">
+        <v>174</v>
+      </c>
+      <c r="E100" t="s">
+        <v>639</v>
+      </c>
+      <c r="F100" t="s">
+        <v>640</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>642</v>
+      </c>
+      <c r="B101" t="s">
+        <v>643</v>
+      </c>
+      <c r="C101" t="s">
+        <v>214</v>
+      </c>
+      <c r="D101" t="s">
+        <v>174</v>
+      </c>
+      <c r="E101" t="s">
+        <v>644</v>
+      </c>
+      <c r="F101" t="s">
+        <v>645</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>647</v>
+      </c>
+      <c r="B102" t="s">
+        <v>648</v>
+      </c>
+      <c r="C102" t="s">
+        <v>649</v>
+      </c>
+      <c r="D102" t="s">
+        <v>183</v>
+      </c>
+      <c r="E102" t="s">
+        <v>650</v>
+      </c>
+      <c r="F102" t="s">
+        <v>472</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>652</v>
+      </c>
+      <c r="B103" t="s">
+        <v>653</v>
+      </c>
+      <c r="C103" t="s">
+        <v>166</v>
+      </c>
+      <c r="D103" t="s">
+        <v>183</v>
+      </c>
+      <c r="E103" t="s">
+        <v>654</v>
+      </c>
+      <c r="F103" t="s">
+        <v>655</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>657</v>
+      </c>
+      <c r="B104" t="s">
+        <v>658</v>
+      </c>
+      <c r="C104" t="s">
+        <v>214</v>
+      </c>
+      <c r="D104" t="s">
+        <v>183</v>
+      </c>
+      <c r="E104" t="s">
+        <v>659</v>
+      </c>
+      <c r="F104" t="s">
+        <v>660</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>662</v>
+      </c>
+      <c r="B105" t="s">
+        <v>663</v>
+      </c>
+      <c r="C105" t="s">
+        <v>254</v>
+      </c>
+      <c r="D105" t="s">
+        <v>183</v>
+      </c>
+      <c r="E105" t="s">
+        <v>664</v>
+      </c>
+      <c r="F105" t="s">
+        <v>665</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>667</v>
+      </c>
+      <c r="B106" t="s">
+        <v>668</v>
+      </c>
+      <c r="C106" t="s">
+        <v>166</v>
+      </c>
+      <c r="D106" t="s">
+        <v>499</v>
+      </c>
+      <c r="E106" t="s">
+        <v>669</v>
+      </c>
+      <c r="F106" t="s">
+        <v>670</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>672</v>
+      </c>
+      <c r="B107" t="s">
+        <v>673</v>
+      </c>
+      <c r="C107" t="s">
+        <v>287</v>
+      </c>
+      <c r="D107" t="s">
+        <v>266</v>
+      </c>
+      <c r="E107" t="s">
+        <v>176</v>
+      </c>
+      <c r="F107" t="s">
+        <v>674</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>676</v>
+      </c>
+      <c r="B108" t="s">
+        <v>677</v>
+      </c>
+      <c r="C108" t="s">
+        <v>228</v>
+      </c>
+      <c r="D108" t="s">
+        <v>183</v>
+      </c>
+      <c r="E108" t="s">
+        <v>678</v>
+      </c>
+      <c r="F108" t="s">
+        <v>679</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>681</v>
+      </c>
+      <c r="B109" t="s">
+        <v>682</v>
+      </c>
+      <c r="C109" t="s">
+        <v>293</v>
+      </c>
+      <c r="D109" t="s">
+        <v>183</v>
+      </c>
+      <c r="E109" t="s">
+        <v>683</v>
+      </c>
+      <c r="F109" t="s">
+        <v>684</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>686</v>
+      </c>
+      <c r="B110" t="s">
+        <v>687</v>
+      </c>
+      <c r="C110" t="s">
+        <v>214</v>
+      </c>
+      <c r="D110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E110" t="s">
+        <v>688</v>
+      </c>
+      <c r="F110" t="s">
+        <v>689</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>691</v>
+      </c>
+      <c r="B111" t="s">
+        <v>692</v>
+      </c>
+      <c r="C111" t="s">
+        <v>693</v>
+      </c>
+      <c r="D111" t="s">
+        <v>183</v>
+      </c>
+      <c r="E111" t="s">
+        <v>694</v>
+      </c>
+      <c r="F111" t="s">
+        <v>695</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>697</v>
+      </c>
+      <c r="B112" t="s">
+        <v>698</v>
+      </c>
+      <c r="C112" t="s">
+        <v>699</v>
+      </c>
+      <c r="D112" t="s">
+        <v>183</v>
+      </c>
+      <c r="E112" t="s">
+        <v>700</v>
+      </c>
+      <c r="F112" t="s">
+        <v>701</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>703</v>
+      </c>
+      <c r="B113" t="s">
+        <v>704</v>
+      </c>
+      <c r="C113" t="s">
+        <v>210</v>
+      </c>
+      <c r="D113" t="s">
+        <v>183</v>
+      </c>
+      <c r="E113" t="s">
+        <v>705</v>
+      </c>
+      <c r="F113" t="s">
+        <v>289</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>707</v>
+      </c>
+      <c r="B114" t="s">
+        <v>708</v>
+      </c>
+      <c r="C114" t="s">
+        <v>214</v>
+      </c>
+      <c r="D114" t="s">
+        <v>183</v>
+      </c>
+      <c r="E114" t="s">
+        <v>709</v>
+      </c>
+      <c r="F114" t="s">
+        <v>710</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>712</v>
+      </c>
+      <c r="B115" t="s">
+        <v>708</v>
+      </c>
+      <c r="C115" t="s">
+        <v>713</v>
+      </c>
+      <c r="D115" t="s">
+        <v>183</v>
+      </c>
+      <c r="E115" t="s">
+        <v>221</v>
+      </c>
+      <c r="F115" t="s">
+        <v>714</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>716</v>
+      </c>
+      <c r="B116" t="s">
+        <v>704</v>
+      </c>
+      <c r="C116" t="s">
+        <v>210</v>
+      </c>
+      <c r="D116" t="s">
+        <v>183</v>
+      </c>
+      <c r="E116" t="s">
+        <v>717</v>
+      </c>
+      <c r="F116" t="s">
+        <v>718</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>720</v>
+      </c>
+      <c r="B117" t="s">
+        <v>721</v>
+      </c>
+      <c r="C117" t="s">
+        <v>722</v>
+      </c>
+      <c r="D117" t="s">
+        <v>183</v>
+      </c>
+      <c r="E117" t="s">
+        <v>723</v>
+      </c>
+      <c r="F117" t="s">
+        <v>724</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>726</v>
+      </c>
+      <c r="B118" t="s">
+        <v>727</v>
+      </c>
+      <c r="C118" t="s">
+        <v>728</v>
+      </c>
+      <c r="D118" t="s">
+        <v>183</v>
+      </c>
+      <c r="E118" t="s">
+        <v>729</v>
+      </c>
+      <c r="F118" t="s">
+        <v>730</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>732</v>
+      </c>
+      <c r="B119" t="s">
+        <v>733</v>
+      </c>
+      <c r="C119" t="s">
+        <v>734</v>
+      </c>
+      <c r="D119" t="s">
+        <v>499</v>
+      </c>
+      <c r="E119" t="s">
+        <v>176</v>
+      </c>
+      <c r="F119" t="s">
+        <v>735</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>737</v>
+      </c>
+      <c r="B120" t="s">
+        <v>738</v>
+      </c>
+      <c r="C120" t="s">
+        <v>293</v>
+      </c>
+      <c r="D120" t="s">
+        <v>183</v>
+      </c>
+      <c r="E120" t="s">
+        <v>739</v>
+      </c>
+      <c r="F120" t="s">
+        <v>701</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>741</v>
+      </c>
+      <c r="B121" t="s">
+        <v>742</v>
+      </c>
+      <c r="C121" t="s">
+        <v>293</v>
+      </c>
+      <c r="D121" t="s">
+        <v>183</v>
+      </c>
+      <c r="E121" t="s">
+        <v>743</v>
+      </c>
+      <c r="F121" t="s">
+        <v>744</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>746</v>
+      </c>
+      <c r="B122" t="s">
+        <v>747</v>
+      </c>
+      <c r="C122" t="s">
+        <v>293</v>
+      </c>
+      <c r="D122" t="s">
+        <v>183</v>
+      </c>
+      <c r="E122" t="s">
+        <v>748</v>
+      </c>
+      <c r="F122" t="s">
+        <v>283</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>750</v>
+      </c>
+      <c r="B123" t="s">
+        <v>751</v>
+      </c>
+      <c r="C123" t="s">
+        <v>752</v>
+      </c>
+      <c r="D123" t="s">
+        <v>183</v>
+      </c>
+      <c r="E123" t="s">
+        <v>753</v>
+      </c>
+      <c r="F123" t="s">
+        <v>754</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>756</v>
+      </c>
+      <c r="B124" t="s">
+        <v>751</v>
+      </c>
+      <c r="C124" t="s">
+        <v>752</v>
+      </c>
+      <c r="D124" t="s">
+        <v>183</v>
+      </c>
+      <c r="E124" t="s">
+        <v>757</v>
+      </c>
+      <c r="F124" t="s">
+        <v>758</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>760</v>
+      </c>
+      <c r="B125" t="s">
+        <v>761</v>
+      </c>
+      <c r="C125" t="s">
+        <v>166</v>
+      </c>
+      <c r="D125" t="s">
+        <v>183</v>
+      </c>
+      <c r="E125" t="s">
+        <v>762</v>
+      </c>
+      <c r="F125" t="s">
+        <v>763</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>765</v>
+      </c>
+      <c r="B126" t="s">
+        <v>766</v>
+      </c>
+      <c r="C126" t="s">
+        <v>767</v>
+      </c>
+      <c r="D126" t="s">
+        <v>174</v>
+      </c>
+      <c r="E126" t="s">
+        <v>768</v>
+      </c>
+      <c r="F126" t="s">
+        <v>769</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>771</v>
+      </c>
+      <c r="B127" t="s">
+        <v>772</v>
+      </c>
+      <c r="C127" t="s">
+        <v>214</v>
+      </c>
+      <c r="D127" t="s">
+        <v>183</v>
+      </c>
+      <c r="E127" t="s">
+        <v>773</v>
+      </c>
+      <c r="F127" t="s">
+        <v>774</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>776</v>
+      </c>
+      <c r="B128" t="s">
+        <v>777</v>
+      </c>
+      <c r="C128" t="s">
+        <v>214</v>
+      </c>
+      <c r="D128" t="s">
+        <v>183</v>
+      </c>
+      <c r="E128" t="s">
+        <v>778</v>
+      </c>
+      <c r="F128" t="s">
+        <v>779</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>781</v>
+      </c>
+      <c r="B129" t="s">
+        <v>761</v>
+      </c>
+      <c r="C129" t="s">
+        <v>166</v>
+      </c>
+      <c r="D129" t="s">
+        <v>183</v>
+      </c>
+      <c r="E129" t="s">
+        <v>782</v>
+      </c>
+      <c r="F129" t="s">
+        <v>763</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>784</v>
+      </c>
+      <c r="B130" t="s">
+        <v>383</v>
+      </c>
+      <c r="C130" t="s">
+        <v>166</v>
+      </c>
+      <c r="D130" t="s">
+        <v>183</v>
+      </c>
+      <c r="E130" t="s">
+        <v>304</v>
+      </c>
+      <c r="F130" t="s">
+        <v>385</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>786</v>
+      </c>
+      <c r="B131" t="s">
+        <v>383</v>
+      </c>
+      <c r="C131" t="s">
+        <v>166</v>
+      </c>
+      <c r="D131" t="s">
+        <v>183</v>
+      </c>
+      <c r="E131" t="s">
+        <v>304</v>
+      </c>
+      <c r="F131" t="s">
+        <v>385</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>788</v>
+      </c>
+      <c r="B132" t="s">
+        <v>789</v>
+      </c>
+      <c r="C132" t="s">
+        <v>790</v>
+      </c>
+      <c r="D132" t="s">
+        <v>499</v>
+      </c>
+      <c r="E132" t="s">
+        <v>791</v>
+      </c>
+      <c r="F132" t="s">
+        <v>792</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>794</v>
+      </c>
+      <c r="B133" t="s">
+        <v>795</v>
+      </c>
+      <c r="C133" t="s">
+        <v>796</v>
+      </c>
+      <c r="D133" t="s">
+        <v>281</v>
+      </c>
+      <c r="E133" t="s">
+        <v>797</v>
+      </c>
+      <c r="F133" t="s">
+        <v>798</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>800</v>
+      </c>
+      <c r="B134" t="s">
+        <v>801</v>
+      </c>
+      <c r="C134" t="s">
+        <v>802</v>
+      </c>
+      <c r="D134" t="s">
+        <v>183</v>
+      </c>
+      <c r="E134" t="s">
+        <v>803</v>
+      </c>
+      <c r="F134" t="s">
+        <v>804</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>806</v>
+      </c>
+      <c r="B135" t="s">
+        <v>807</v>
+      </c>
+      <c r="C135" t="s">
+        <v>808</v>
+      </c>
+      <c r="D135" t="s">
+        <v>183</v>
+      </c>
+      <c r="E135" t="s">
+        <v>809</v>
+      </c>
+      <c r="F135" t="s">
+        <v>810</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>812</v>
+      </c>
+      <c r="B136" t="s">
+        <v>813</v>
+      </c>
+      <c r="C136" t="s">
+        <v>814</v>
+      </c>
+      <c r="D136" t="s">
+        <v>183</v>
+      </c>
+      <c r="E136" t="s">
+        <v>815</v>
+      </c>
+      <c r="F136" t="s">
+        <v>816</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>812</v>
+      </c>
+      <c r="B137" t="s">
+        <v>813</v>
+      </c>
+      <c r="C137" t="s">
+        <v>818</v>
+      </c>
+      <c r="D137" t="s">
+        <v>183</v>
+      </c>
+      <c r="E137" t="s">
+        <v>815</v>
+      </c>
+      <c r="F137" t="s">
+        <v>816</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>820</v>
+      </c>
+      <c r="B138" t="s">
+        <v>821</v>
+      </c>
+      <c r="C138" t="s">
+        <v>822</v>
+      </c>
+      <c r="D138" t="s">
+        <v>183</v>
+      </c>
+      <c r="E138" t="s">
+        <v>221</v>
+      </c>
+      <c r="F138" t="s">
+        <v>823</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>825</v>
+      </c>
+      <c r="B139" t="s">
+        <v>336</v>
+      </c>
+      <c r="C139" t="s">
+        <v>337</v>
+      </c>
+      <c r="D139" t="s">
+        <v>183</v>
+      </c>
+      <c r="E139" t="s">
+        <v>176</v>
+      </c>
+      <c r="F139" t="s">
+        <v>176</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>827</v>
+      </c>
+      <c r="B140" t="s">
+        <v>828</v>
+      </c>
+      <c r="C140" t="s">
+        <v>829</v>
+      </c>
+      <c r="D140" t="s">
+        <v>183</v>
+      </c>
+      <c r="E140" t="s">
+        <v>830</v>
+      </c>
+      <c r="F140" t="s">
+        <v>831</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>833</v>
+      </c>
+      <c r="B141" t="s">
+        <v>834</v>
+      </c>
+      <c r="C141" t="s">
+        <v>835</v>
+      </c>
+      <c r="D141" t="s">
+        <v>183</v>
+      </c>
+      <c r="E141" t="s">
+        <v>836</v>
+      </c>
+      <c r="F141" t="s">
+        <v>837</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>839</v>
+      </c>
+      <c r="B142" t="s">
+        <v>840</v>
+      </c>
+      <c r="C142" t="s">
+        <v>214</v>
+      </c>
+      <c r="D142" t="s">
+        <v>183</v>
+      </c>
+      <c r="E142" t="s">
+        <v>841</v>
+      </c>
+      <c r="F142" t="s">
+        <v>273</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>843</v>
+      </c>
+      <c r="B143" t="s">
+        <v>365</v>
+      </c>
+      <c r="C143" t="s">
+        <v>844</v>
+      </c>
+      <c r="D143" t="s">
+        <v>183</v>
+      </c>
+      <c r="E143" t="s">
+        <v>845</v>
+      </c>
+      <c r="F143" t="s">
+        <v>846</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>848</v>
+      </c>
+      <c r="B144" t="s">
+        <v>849</v>
+      </c>
+      <c r="C144" t="s">
+        <v>214</v>
+      </c>
+      <c r="D144" t="s">
+        <v>183</v>
+      </c>
+      <c r="E144" t="s">
+        <v>850</v>
+      </c>
+      <c r="F144" t="s">
+        <v>851</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>853</v>
+      </c>
+      <c r="B145" t="s">
+        <v>854</v>
+      </c>
+      <c r="C145" t="s">
+        <v>564</v>
+      </c>
+      <c r="D145" t="s">
+        <v>183</v>
+      </c>
+      <c r="E145" t="s">
+        <v>176</v>
+      </c>
+      <c r="F145" t="s">
+        <v>855</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>857</v>
+      </c>
+      <c r="B146" t="s">
+        <v>336</v>
+      </c>
+      <c r="C146" t="s">
+        <v>337</v>
+      </c>
+      <c r="D146" t="s">
+        <v>183</v>
+      </c>
+      <c r="E146" t="s">
+        <v>176</v>
+      </c>
+      <c r="F146" t="s">
+        <v>176</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>859</v>
+      </c>
+      <c r="B147" t="s">
+        <v>860</v>
+      </c>
+      <c r="C147" t="s">
+        <v>861</v>
+      </c>
+      <c r="D147" t="s">
+        <v>183</v>
+      </c>
+      <c r="E147" t="s">
+        <v>560</v>
+      </c>
+      <c r="F147" t="s">
+        <v>862</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>864</v>
+      </c>
+      <c r="B148" t="s">
+        <v>865</v>
+      </c>
+      <c r="C148" t="s">
+        <v>166</v>
+      </c>
+      <c r="D148" t="s">
+        <v>499</v>
+      </c>
+      <c r="E148" t="s">
+        <v>866</v>
+      </c>
+      <c r="F148" t="s">
+        <v>867</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>869</v>
+      </c>
+      <c r="B149" t="s">
+        <v>870</v>
+      </c>
+      <c r="C149" t="s">
+        <v>790</v>
+      </c>
+      <c r="D149" t="s">
+        <v>183</v>
+      </c>
+      <c r="E149" t="s">
+        <v>871</v>
+      </c>
+      <c r="F149" t="s">
+        <v>872</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>874</v>
+      </c>
+      <c r="B150" t="s">
+        <v>292</v>
+      </c>
+      <c r="C150" t="s">
+        <v>293</v>
+      </c>
+      <c r="D150" t="s">
+        <v>183</v>
+      </c>
+      <c r="E150" t="s">
+        <v>875</v>
+      </c>
+      <c r="F150" t="s">
+        <v>876</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>878</v>
+      </c>
+      <c r="B151" t="s">
+        <v>663</v>
+      </c>
+      <c r="C151" t="s">
+        <v>254</v>
+      </c>
+      <c r="D151" t="s">
+        <v>183</v>
+      </c>
+      <c r="E151" t="s">
+        <v>879</v>
+      </c>
+      <c r="F151" t="s">
+        <v>665</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>881</v>
+      </c>
+      <c r="B152" t="s">
+        <v>882</v>
+      </c>
+      <c r="C152" t="s">
+        <v>883</v>
+      </c>
+      <c r="D152" t="s">
+        <v>183</v>
+      </c>
+      <c r="E152" t="s">
+        <v>884</v>
+      </c>
+      <c r="F152" t="s">
+        <v>885</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>887</v>
+      </c>
+      <c r="B153" t="s">
+        <v>888</v>
+      </c>
+      <c r="C153" t="s">
+        <v>889</v>
+      </c>
+      <c r="D153" t="s">
+        <v>183</v>
+      </c>
+      <c r="E153" t="s">
+        <v>890</v>
+      </c>
+      <c r="F153" t="s">
+        <v>494</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>892</v>
+      </c>
+      <c r="B154" t="s">
+        <v>893</v>
+      </c>
+      <c r="C154" t="s">
+        <v>790</v>
+      </c>
+      <c r="D154" t="s">
+        <v>183</v>
+      </c>
+      <c r="E154" t="s">
+        <v>894</v>
+      </c>
+      <c r="F154" t="s">
+        <v>305</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>895</v>
       </c>
     </row>
   </sheetData>
@@ -4886,6 +7555,78 @@
     <hyperlink ref="H80" r:id="rId79"/>
     <hyperlink ref="H81" r:id="rId80"/>
     <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
+    <hyperlink ref="H149" r:id="rId148"/>
+    <hyperlink ref="H150" r:id="rId149"/>
+    <hyperlink ref="H151" r:id="rId150"/>
+    <hyperlink ref="H152" r:id="rId151"/>
+    <hyperlink ref="H153" r:id="rId152"/>
+    <hyperlink ref="H154" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
